--- a/work/WP_SEO_AI_Scenario_Planning.xlsx
+++ b/work/WP_SEO_AI_Scenario_Planning.xlsx
@@ -3084,7 +3084,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Deal cycle: 2 months (SQL → close). SQLs row shows when pipeline must be generated.</t>
+          <t>Deal cycle: 2 months (SQL → close). Pipeline row shows when SQLs must be generated.</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Martijn: 0.6 FTE Apr-Jul, 0.5 FTE Aug+. Victor: 0.2→1.0 FTE (Jun for baseline/push, May for hyper-push).</t>
+          <t>Martijn: 0.6 FTE Apr-Jul, 0.5 FTE Aug+. Victor: 0.2→1.0 FTE (Jun baseline/push, May hyper-push).</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>Hit €2M — hire ahead of pipeline</t>
+          <t>Hit €2M — staggered hiring, controlled acceleration</t>
         </is>
       </c>
     </row>
@@ -4292,21 +4292,21 @@
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>We move faster: Victor full-time in June, two new AEs in July, a third in September. Martijn goes 0.5 FTE in August. BDR scales to 5 by Q4 with the SMB team contributing ~15 meetings/month on top. This gives us 4+ effective AEs by October — enough to run the full deal cadence across all three tiers.</t>
+          <t>The push scenario targets €2M new deal ARR with a measured ramp. Victor goes full-time in June. First new AE joins in July, a second in August, and a third in October — staggered to avoid overloading the pipeline and giving each hire time to absorb the narrative before the next one arrives. Martijn shifts to 0.5 FTE in August.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>The bet: we can source and qualify enough MM pipeline to fill these seats. The dedicated BDR team needs to deliver 70 meetings/month by Q4, on top of the 15 from SMB spillover. That's 85 qualified MM meetings monthly. At 10% close rate, that's 8-9 deals/month closing by Q4.</t>
+          <t>BDR scales to 4 by Q3 and 5 by Q4, supplemented by ~15 MM meetings/month from the SMB team. By October we have 4+ effective AEs producing. The deal cadence compounds: Q4 alone delivers roughly 40% of the total ARR as the hiring investments from Q3 hit full productivity.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>Risk profile: MEDIUM. Monthly burn peaks at €46K. We're hiring 4 new AEs before the first pilot cohort converts (Sep). If conversion disappoints, we're carrying cost against an unproven thesis. But if the motion works, push gets us to €2.4M new deal ARR and €2.5M total — well past the €2M target with room to overachieve.</t>
+          <t>Risk profile: MEDIUM. Monthly burn peaks at €38K. Three new AEs is a meaningful investment but not a bet-the-farm move. The staggered start gives us an exit ramp — if the first hire (July) underperforms by August, we can delay or redirect the October hire. If close rates hold at 10%, we land right at €2M. Expansion from pilot conversions adds upside toward €2.1M+.</t>
         </is>
       </c>
     </row>
@@ -4442,25 +4442,25 @@
         <v>0</v>
       </c>
       <c r="F69" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="25" t="n">
         <v>2</v>
       </c>
       <c r="H69" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I69" s="25" t="n">
+      <c r="K69" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J69" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="K69" s="25" t="n">
-        <v>4</v>
-      </c>
       <c r="L69" s="26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4491,37 +4491,37 @@
       </c>
       <c r="F70" s="27" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="G70" s="27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="H70" s="27" t="inlineStr">
         <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I70" s="27" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J70" s="27" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="I70" s="27" t="inlineStr">
+      <c r="K70" s="27" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="J70" s="27" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="K70" s="27" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
       <c r="L70" s="26" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="F72" s="27" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="G72" s="27" t="inlineStr">
@@ -4600,22 +4600,22 @@
       </c>
       <c r="H72" s="27" t="inlineStr">
         <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="I72" s="27" t="inlineStr">
+        <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="I72" s="27" t="inlineStr">
+      <c r="J72" s="27" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="J72" s="27" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
       <c r="K72" s="27" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="L72" s="26" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="F73" s="28" t="inlineStr">
         <is>
-          <t>€33.6k</t>
+          <t>€27.6k</t>
         </is>
       </c>
       <c r="G73" s="28" t="inlineStr">
@@ -4657,27 +4657,27 @@
       </c>
       <c r="H73" s="28" t="inlineStr">
         <is>
-          <t>€43.0k</t>
+          <t>€37.0k</t>
         </is>
       </c>
       <c r="I73" s="28" t="inlineStr">
         <is>
+          <t>€41.0k</t>
+        </is>
+      </c>
+      <c r="J73" s="28" t="inlineStr">
+        <is>
           <t>€47.0k</t>
         </is>
       </c>
-      <c r="J73" s="28" t="inlineStr">
-        <is>
-          <t>€53.0k</t>
-        </is>
-      </c>
       <c r="K73" s="28" t="inlineStr">
         <is>
-          <t>€53.0k</t>
+          <t>€47.0k</t>
         </is>
       </c>
       <c r="L73" s="26" t="inlineStr">
         <is>
-          <t>€299k total</t>
+          <t>€269k total</t>
         </is>
       </c>
     </row>
@@ -4772,25 +4772,25 @@
         <v>3</v>
       </c>
       <c r="F77" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" s="28" t="n">
         <v>6</v>
       </c>
       <c r="H77" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I77" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J77" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="I77" s="28" t="n">
+      <c r="K77" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="J77" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="K77" s="28" t="n">
-        <v>10</v>
-      </c>
       <c r="L77" s="26" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78">
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="28" t="n">
         <v>2</v>
@@ -4829,10 +4829,10 @@
         <v>2</v>
       </c>
       <c r="K78" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L78" s="26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -4868,13 +4868,13 @@
         <v>1</v>
       </c>
       <c r="J79" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -4893,25 +4893,25 @@
         <v>5</v>
       </c>
       <c r="F80" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G80" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H80" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="H80" s="27" t="n">
+      <c r="I80" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="I80" s="27" t="n">
+      <c r="K80" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="J80" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="K80" s="27" t="n">
-        <v>15</v>
-      </c>
       <c r="L80" s="26" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82">
@@ -5025,25 +5025,25 @@
         <v>5</v>
       </c>
       <c r="H84" s="30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I84" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J84" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="J84" s="30" t="n">
+      <c r="K84" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L84" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="K84" s="30" t="n">
+      <c r="M84" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="L84" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="M84" s="30" t="n">
-        <v>15</v>
-      </c>
       <c r="N84" s="29" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85">
@@ -5067,23 +5067,23 @@
         <v>50</v>
       </c>
       <c r="F85" s="43" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G85" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="H85" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="H85" s="43" t="n">
+      <c r="I85" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J85" s="43" t="n">
         <v>110</v>
       </c>
-      <c r="I85" s="43" t="n">
+      <c r="K85" s="43" t="n">
         <v>110</v>
       </c>
-      <c r="J85" s="43" t="n">
-        <v>140</v>
-      </c>
-      <c r="K85" s="43" t="n">
-        <v>150</v>
-      </c>
       <c r="L85" s="43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="N85" s="44" t="n">
-        <v>760</v>
+        <v>640</v>
       </c>
     </row>
     <row r="87">
@@ -5186,37 +5186,37 @@
       </c>
       <c r="F89" s="30" t="inlineStr">
         <is>
-          <t>€225k</t>
+          <t>€210k</t>
         </is>
       </c>
       <c r="G89" s="30" t="inlineStr">
         <is>
+          <t>€240k</t>
+        </is>
+      </c>
+      <c r="H89" s="30" t="inlineStr">
+        <is>
           <t>€290k</t>
         </is>
       </c>
-      <c r="H89" s="30" t="inlineStr">
+      <c r="I89" s="30" t="inlineStr">
+        <is>
+          <t>€305k</t>
+        </is>
+      </c>
+      <c r="J89" s="30" t="inlineStr">
         <is>
           <t>€320k</t>
         </is>
       </c>
-      <c r="I89" s="30" t="inlineStr">
+      <c r="K89" s="30" t="inlineStr">
         <is>
           <t>€320k</t>
         </is>
       </c>
-      <c r="J89" s="30" t="inlineStr">
-        <is>
-          <t>€450k</t>
-        </is>
-      </c>
-      <c r="K89" s="30" t="inlineStr">
-        <is>
-          <t>€500k</t>
-        </is>
-      </c>
       <c r="L89" s="29" t="inlineStr">
         <is>
-          <t>€2.36M</t>
+          <t>€1.94M</t>
         </is>
       </c>
     </row>
@@ -5230,54 +5230,54 @@
         <f> €2M target</f>
         <v/>
       </c>
-      <c r="C90" s="38" t="inlineStr">
+      <c r="C90" s="31" t="inlineStr">
         <is>
           <t>€30k</t>
         </is>
       </c>
-      <c r="D90" s="38" t="inlineStr">
+      <c r="D90" s="31" t="inlineStr">
         <is>
           <t>€60k</t>
         </is>
       </c>
-      <c r="E90" s="38" t="inlineStr">
+      <c r="E90" s="31" t="inlineStr">
         <is>
           <t>€255k</t>
         </is>
       </c>
-      <c r="F90" s="38" t="inlineStr">
-        <is>
-          <t>€480k</t>
-        </is>
-      </c>
-      <c r="G90" s="38" t="inlineStr">
-        <is>
-          <t>€770k</t>
-        </is>
-      </c>
-      <c r="H90" s="38" t="inlineStr">
-        <is>
-          <t>€1.09M</t>
-        </is>
-      </c>
-      <c r="I90" s="38" t="inlineStr">
-        <is>
-          <t>€1.41M</t>
-        </is>
-      </c>
-      <c r="J90" s="38" t="inlineStr">
-        <is>
-          <t>€1.86M</t>
-        </is>
-      </c>
-      <c r="K90" s="38" t="inlineStr">
-        <is>
-          <t>€2.36M</t>
-        </is>
-      </c>
-      <c r="L90" s="41" t="inlineStr">
-        <is>
-          <t>€2.36M</t>
+      <c r="F90" s="31" t="inlineStr">
+        <is>
+          <t>€465k</t>
+        </is>
+      </c>
+      <c r="G90" s="31" t="inlineStr">
+        <is>
+          <t>€705k</t>
+        </is>
+      </c>
+      <c r="H90" s="31" t="inlineStr">
+        <is>
+          <t>€995k</t>
+        </is>
+      </c>
+      <c r="I90" s="31" t="inlineStr">
+        <is>
+          <t>€1.30M</t>
+        </is>
+      </c>
+      <c r="J90" s="31" t="inlineStr">
+        <is>
+          <t>€1.62M</t>
+        </is>
+      </c>
+      <c r="K90" s="31" t="inlineStr">
+        <is>
+          <t>€1.94M</t>
+        </is>
+      </c>
+      <c r="L90" s="32" t="inlineStr">
+        <is>
+          <t>€1.94M</t>
         </is>
       </c>
     </row>
@@ -5366,37 +5366,37 @@
       </c>
       <c r="F92" s="35" t="inlineStr">
         <is>
-          <t>€480k</t>
+          <t>€465k</t>
         </is>
       </c>
       <c r="G92" s="35" t="inlineStr">
         <is>
-          <t>€770k</t>
+          <t>€705k</t>
         </is>
       </c>
       <c r="H92" s="35" t="inlineStr">
         <is>
-          <t>€1.12M</t>
+          <t>€1.03M</t>
         </is>
       </c>
       <c r="I92" s="35" t="inlineStr">
         <is>
-          <t>€1.48M</t>
+          <t>€1.37M</t>
         </is>
       </c>
       <c r="J92" s="35" t="inlineStr">
         <is>
-          <t>€1.97M</t>
+          <t>€1.73M</t>
         </is>
       </c>
       <c r="K92" s="35" t="inlineStr">
         <is>
-          <t>€2.54M</t>
+          <t>€2.12M</t>
         </is>
       </c>
       <c r="L92" s="36" t="inlineStr">
         <is>
-          <t>€2.54M</t>
+          <t>€2.12M</t>
         </is>
       </c>
     </row>
@@ -5410,20 +5410,20 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>76 deals ÷ 10% = 760 meetings needed over 9 months</t>
+          <t>64 deals ÷ 10% = 640 meetings needed over 9 months</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18">
-        <f> 85 meetings/month − 15 from SMB BDRs = 70 from dedicated BDRs</f>
+        <f> 72 meetings/month − 15 from SMB BDRs = 57 from dedicated BDRs</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="37" t="inlineStr">
         <is>
-          <t>70/mo ÷ 15/BDR = 5 dedicated MM BDRs needed</t>
+          <t>57/mo ÷ 15/BDR = 4 dedicated MM BDRs needed</t>
         </is>
       </c>
     </row>

--- a/work/WP_SEO_AI_Scenario_Planning.xlsx
+++ b/work/WP_SEO_AI_Scenario_Planning.xlsx
@@ -226,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,6 +312,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3008,7 +3011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3070,35 +3073,35 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Blended close rate: 10% (meeting → deal). Deal type determined during sales process.</t>
+          <t>Martijn: max 0.5 FTE throughout. Victor: 0.2 FTE → 1.0 FTE (Jun for baseline/push, May for hyper-push).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>SMB BDR team contributes ~15 MM meetings/month (free pipeline).</t>
+          <t>Blended close rate: 10% (meeting → deal). Deal type determined during sales process.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Deal cycle: 2 months (SQL → close). Pipeline row shows when SQLs must be generated.</t>
+          <t>SMB BDR team contributes ~15 MM meetings/month (free pipeline).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>Pilot conversion at month 5: 40% → Medium, 10% → Large. Expansion = upside, not counted toward €2M.</t>
+          <t>Deal cycle: 2 months (SQL → close). Pipeline row shows when SQLs must be generated.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Martijn: 0.6 FTE Apr-Jul, 0.5 FTE Aug+. Victor: 0.2→1.0 FTE (Jun baseline/push, May hyper-push).</t>
+          <t>Pilot conversion at month 5: 40% → Medium, 10% → Large. Expansion = upside, not counted toward €2M.</t>
         </is>
       </c>
     </row>
@@ -3109,582 +3112,547 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Push/Hyper scenarios include 1 large deal closing in May (currently in advanced pipeline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 1: BASELINE</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Conservative ramp — prove the motion, then scale</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>NARRATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>We start with 0.8 FTE AE capacity (Martijn 0.6 + Victor 0.2) and 0.4 FTE BDR. Victor goes full-time in June, giving us 1.6 effective AEs by mid-Q2. One new AE joins in July, ramping through Q3. Martijn shifts to 0.5 FTE in August as leadership duties grow. A second new hire follows in October. BDR scales to 3 by Q4, supplemented by ~15 MM meetings/month from the SMB BDR team.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>This is the 'prove it before you scale' path. We close our first pilots in May-June, get the narrative tested in 20+ meetings before hiring aggressively, and let the month-5 pilot reviews (starting September) validate the conversion thesis. If pilot conversion lands at 40%+, we have the signal to accelerate into 2027.</t>
+          <t>We start with 0.7 FTE AE capacity (Martijn 0.5 + Victor 0.2) and 0.4 FTE BDR. Victor goes full-time in June, giving us 1.5 effective AEs. One new AE joins in July, ramping through Q3. A second new hire follows in October. BDR scales to 3 by Q4, supplemented by ~15 MM meetings/month from the SMB BDR team.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>Risk profile: LOW. Total cost €185K over 9 months. If the motion stalls, we've spent less than a single enterprise AE's annual package. Downside: we land at €1.7M — short of €2M but with a clean foundation. The expansion revenue from pilot conversions adds €175K upside, bringing total ARR to €1.9M. The gap tells us exactly how much to accelerate in Q1 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+          <t>This is the 'prove it before you scale' path. We close our first pilots in May-June, get the narrative tested in 20+ meetings before hiring aggressively, and let the month-5 pilot reviews (starting September) validate the conversion thesis. If pilot conversion lands at 40%+, we have the signal to accelerate into 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Risk profile: LOW. Total cost under €185K over 9 months. Downside: we land around €1.6M — short of €2M but with a clean foundation and proven playbook. Expansion from pilot conversions adds upside. The gap tells us exactly how much to accelerate in Q1 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L25" s="22" t="inlineStr">
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C26" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F26" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G26" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H26" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I26" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J26" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K26" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L26" s="26" t="n">
-        <v>1.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>AEs (new hires)</t>
+          <t>AEs (ramped)</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>cumulative</t>
+          <t>FTE</t>
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F27" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J27" s="25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L27" s="26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Effective AEs</t>
+          <t>AEs (new hires)</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D28" s="27" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G28" s="27" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="I28" s="27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K28" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="L28" s="26" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
+          <t>Effective AEs</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" s="26" t="n">
-        <v>3</v>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I29" s="27" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J29" s="27" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D30" s="27" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="G30" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="I30" s="27" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="K30" s="27" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="L30" s="26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D30" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I31" s="27" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="J31" s="27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K31" s="27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
           <t>Monthly cost</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>€6.4k</t>
-        </is>
-      </c>
-      <c r="D31" s="28" t="inlineStr">
-        <is>
-          <t>€6.4k</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>€13.6k</t>
-        </is>
-      </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>€19.6k</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
+        <is>
+          <t>€5.8k</t>
+        </is>
+      </c>
+      <c r="D32" s="28" t="inlineStr">
+        <is>
+          <t>€5.8k</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>€13.0k</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
+          <t>€19.0k</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr">
         <is>
           <t>€23.0k</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>€23.0k</t>
         </is>
       </c>
-      <c r="I31" s="28" t="inlineStr">
+      <c r="I32" s="28" t="inlineStr">
         <is>
           <t>€27.0k</t>
         </is>
       </c>
-      <c r="J31" s="28" t="inlineStr">
+      <c r="J32" s="28" t="inlineStr">
         <is>
           <t>€33.0k</t>
         </is>
       </c>
-      <c r="K31" s="28" t="inlineStr">
+      <c r="K32" s="28" t="inlineStr">
         <is>
           <t>€33.0k</t>
         </is>
       </c>
-      <c r="L31" s="26" t="inlineStr">
-        <is>
-          <t>€185k total</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="L32" s="26" t="inlineStr">
+        <is>
+          <t>€183k total</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>DEAL FLOW</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>from AE capacity</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr"/>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr"/>
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J34" s="22" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K34" s="22" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
+      <c r="L35" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Pilots</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C35" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="K35" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="L35" s="26" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Pilots</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>€50K ARR</t>
+          <t>€15K ARR</t>
         </is>
       </c>
       <c r="C36" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G36" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36" s="28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J36" s="28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K36" s="28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L36" s="26" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>€100K ARR</t>
+          <t>€50K ARR</t>
         </is>
       </c>
       <c r="C37" s="28" t="n">
@@ -3709,1141 +3677,1141 @@
         <v>1</v>
       </c>
       <c r="J37" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
         <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
           <t>Total deals closing</t>
         </is>
       </c>
-      <c r="C38" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" s="27" t="n">
+      <c r="C39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G39" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="H39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I38" s="27" t="n">
+      <c r="I39" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="27" t="n">
+      <c r="J39" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="K38" s="27" t="n">
+      <c r="K39" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="26" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="L39" s="26" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>PIPELINE NEEDED</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>2-mo cycle</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr"/>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="B42" s="22" t="inlineStr"/>
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E42" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G42" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H42" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I41" s="22" t="inlineStr">
+      <c r="I42" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J41" s="22" t="inlineStr">
+      <c r="J42" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K41" s="22" t="inlineStr">
+      <c r="K42" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L41" s="22" t="inlineStr">
+      <c r="L42" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M41" s="22" t="inlineStr">
+      <c r="M42" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N41" s="22" t="inlineStr">
+      <c r="N42" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I42" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K42" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L42" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="M42" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="N42" s="29" t="n">
-        <v>53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
+          <t>Deals closing</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>when they close</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L43" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="M43" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="N43" s="29" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
           <t>SQLs needed</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>when to generate</t>
         </is>
       </c>
-      <c r="C43" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="D43" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E43" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="F43" s="43" t="n">
+      <c r="C44" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F44" s="43" t="n">
         <v>60</v>
       </c>
-      <c r="G43" s="43" t="n">
+      <c r="G44" s="43" t="n">
         <v>60</v>
       </c>
-      <c r="H43" s="43" t="n">
+      <c r="H44" s="43" t="n">
         <v>70</v>
       </c>
-      <c r="I43" s="43" t="n">
+      <c r="I44" s="43" t="n">
         <v>70</v>
       </c>
-      <c r="J43" s="43" t="n">
+      <c r="J44" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="K43" s="43" t="n">
+      <c r="K44" s="43" t="n">
         <v>90</v>
       </c>
-      <c r="L43" s="43" t="inlineStr">
+      <c r="L44" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M43" s="43" t="inlineStr">
+      <c r="M44" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N43" s="44" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="N44" s="44" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>ARR WATERFALL</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr"/>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="B47" s="22" t="inlineStr"/>
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E47" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F46" s="22" t="inlineStr">
+      <c r="F47" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G46" s="22" t="inlineStr">
+      <c r="G47" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="H47" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I46" s="22" t="inlineStr">
+      <c r="I47" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J46" s="22" t="inlineStr">
+      <c r="J47" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K46" s="22" t="inlineStr">
+      <c r="K47" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L46" s="22" t="inlineStr">
+      <c r="L47" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C47" s="30" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="E47" s="30" t="inlineStr">
-        <is>
-          <t>€195k</t>
-        </is>
-      </c>
-      <c r="F47" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="G47" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="H47" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="I47" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="J47" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="K47" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="L47" s="29" t="inlineStr">
-        <is>
-          <t>€1.71M</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B48" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D48" s="31" t="inlineStr">
-        <is>
-          <t>€60k</t>
-        </is>
-      </c>
-      <c r="E48" s="31" t="inlineStr">
-        <is>
-          <t>€255k</t>
-        </is>
-      </c>
-      <c r="F48" s="31" t="inlineStr">
-        <is>
-          <t>€465k</t>
-        </is>
-      </c>
-      <c r="G48" s="31" t="inlineStr">
-        <is>
-          <t>€675k</t>
-        </is>
-      </c>
-      <c r="H48" s="31" t="inlineStr">
-        <is>
-          <t>€900k</t>
-        </is>
-      </c>
-      <c r="I48" s="31" t="inlineStr">
-        <is>
-          <t>€1.12M</t>
-        </is>
-      </c>
-      <c r="J48" s="31" t="inlineStr">
-        <is>
-          <t>€1.42M</t>
-        </is>
-      </c>
-      <c r="K48" s="31" t="inlineStr">
-        <is>
-          <t>€1.71M</t>
-        </is>
-      </c>
-      <c r="L48" s="32" t="inlineStr">
-        <is>
-          <t>€1.71M</t>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>€95k</t>
+        </is>
+      </c>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>€225k</t>
+        </is>
+      </c>
+      <c r="I48" s="30" t="inlineStr">
+        <is>
+          <t>€225k</t>
+        </is>
+      </c>
+      <c r="J48" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="K48" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="L48" s="29" t="inlineStr">
+        <is>
+          <t>€1.57M</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C49" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="I49" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="J49" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="K49" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="L49" s="42" t="inlineStr">
-        <is>
-          <t>+€175k</t>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B49" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="inlineStr">
+        <is>
+          <t>€30k</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>€125k</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>€335k</t>
+        </is>
+      </c>
+      <c r="G49" s="31" t="inlineStr">
+        <is>
+          <t>€545k</t>
+        </is>
+      </c>
+      <c r="H49" s="31" t="inlineStr">
+        <is>
+          <t>€770k</t>
+        </is>
+      </c>
+      <c r="I49" s="31" t="inlineStr">
+        <is>
+          <t>€995k</t>
+        </is>
+      </c>
+      <c r="J49" s="31" t="inlineStr">
+        <is>
+          <t>€1.28M</t>
+        </is>
+      </c>
+      <c r="K49" s="31" t="inlineStr">
+        <is>
+          <t>€1.57M</t>
+        </is>
+      </c>
+      <c r="L49" s="32" t="inlineStr">
+        <is>
+          <t>€1.57M</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>upside</t>
+        </is>
+      </c>
+      <c r="C50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="34" t="inlineStr">
+        <is>
+          <t>€35k</t>
+        </is>
+      </c>
+      <c r="K50" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="L50" s="42" t="inlineStr">
+        <is>
+          <t>+€105k</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C50" s="35" t="inlineStr">
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>€30k</t>
         </is>
       </c>
-      <c r="D50" s="35" t="inlineStr">
-        <is>
-          <t>€60k</t>
-        </is>
-      </c>
-      <c r="E50" s="35" t="inlineStr">
-        <is>
-          <t>€255k</t>
-        </is>
-      </c>
-      <c r="F50" s="35" t="inlineStr">
-        <is>
-          <t>€465k</t>
-        </is>
-      </c>
-      <c r="G50" s="35" t="inlineStr">
-        <is>
-          <t>€675k</t>
-        </is>
-      </c>
-      <c r="H50" s="35" t="inlineStr">
-        <is>
-          <t>€935k</t>
-        </is>
-      </c>
-      <c r="I50" s="35" t="inlineStr">
-        <is>
-          <t>€1.20M</t>
-        </is>
-      </c>
-      <c r="J50" s="35" t="inlineStr">
-        <is>
-          <t>€1.52M</t>
-        </is>
-      </c>
-      <c r="K50" s="35" t="inlineStr">
-        <is>
-          <t>€1.88M</t>
-        </is>
-      </c>
-      <c r="L50" s="36" t="inlineStr">
-        <is>
-          <t>€1.88M</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>€125k</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>€335k</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>€545k</t>
+        </is>
+      </c>
+      <c r="H51" s="35" t="inlineStr">
+        <is>
+          <t>€770k</t>
+        </is>
+      </c>
+      <c r="I51" s="35" t="inlineStr">
+        <is>
+          <t>€995k</t>
+        </is>
+      </c>
+      <c r="J51" s="35" t="inlineStr">
+        <is>
+          <t>€1.32M</t>
+        </is>
+      </c>
+      <c r="K51" s="35" t="inlineStr">
+        <is>
+          <t>€1.68M</t>
+        </is>
+      </c>
+      <c r="L51" s="36" t="inlineStr">
+        <is>
+          <t>€1.68M</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>53 deals ÷ 10% = 530 meetings needed over 9 months</t>
-        </is>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" s="18">
-        <f> 59 meetings/month − 15 from SMB BDRs = 44 from dedicated BDRs</f>
-        <v/>
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>50 deals ÷ 10% = 500 meetings over 9 months</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="37" t="inlineStr">
-        <is>
-          <t>44/mo ÷ 15/BDR = 3 dedicated MM BDRs needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A55" s="18">
+        <f> 56/mo − 15 from SMB BDRs = 41 from dedicated BDRs</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t>41/mo ÷ 15/BDR = 3 dedicated MM BDRs needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 2: PUSH</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="19" t="inlineStr">
-        <is>
-          <t>Hit €2M — staggered hiring, controlled acceleration</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>Hit €2M — staggered hiring, one whale in the bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="inlineStr">
         <is>
           <t>NARRATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="21" t="inlineStr">
-        <is>
-          <t>The push scenario targets €2M new deal ARR with a measured ramp. Victor goes full-time in June. First new AE joins in July, a second in August, and a third in October — staggered to avoid overloading the pipeline and giving each hire time to absorb the narrative before the next one arrives. Martijn shifts to 0.5 FTE in August.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>BDR scales to 4 by Q3 and 5 by Q4, supplemented by ~15 MM meetings/month from the SMB team. By October we have 4+ effective AEs producing. The deal cadence compounds: Q4 alone delivers roughly 40% of the total ARR as the hiring investments from Q3 hit full productivity.</t>
+          <t>The push scenario targets €2M new deal ARR with three levers: an early AE hire in June, staggered reinforcements in August and October, and a large deal already in advanced pipeline closing in May. Victor goes full-time in June. Martijn stays at 0.5 FTE throughout.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>Risk profile: MEDIUM. Monthly burn peaks at €38K. Three new AEs is a meaningful investment but not a bet-the-farm move. The staggered start gives us an exit ramp — if the first hire (July) underperforms by August, we can delay or redirect the October hire. If close rates hold at 10%, we land right at €2M. Expansion from pilot conversions adds upside toward €2.1M+.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+          <t>The May large deal (€100K) is not speculative — it's an active opportunity already in late-stage pipeline. This anchors Q2 revenue and buys time for the June AE hire to ramp. By Q4, we have 4+ effective AEs producing across all three tiers. BDR scales to 5 with the SMB team contributing ~15 meetings/month on top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>Risk profile: MEDIUM. The staggered hiring (Jun/Aug/Oct) gives us an exit ramp at each stage. If the June hire underperforms, we delay August. If close rates drop to 7%, we still land around €1.5M. Monthly burn peaks at €38K. But if the motion works and the May deal signals market readiness, we're past €2M with room to accelerate into 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
         <is>
           <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="22" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B67" s="22" t="inlineStr">
+      <c r="B68" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="C68" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D68" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E67" s="22" t="inlineStr">
+      <c r="E68" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F67" s="22" t="inlineStr">
+      <c r="F68" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G67" s="22" t="inlineStr">
+      <c r="G68" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H67" s="22" t="inlineStr">
+      <c r="H68" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I67" s="22" t="inlineStr">
+      <c r="I68" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J67" s="22" t="inlineStr">
+      <c r="J68" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K67" s="22" t="inlineStr">
+      <c r="K68" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L67" s="22" t="inlineStr">
+      <c r="L68" s="22" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C68" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D68" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E68" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F68" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L68" s="26" t="n">
-        <v>1.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>AEs (new hires)</t>
+          <t>AEs (ramped)</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>cumulative</t>
+          <t>FTE</t>
         </is>
       </c>
       <c r="C69" s="25" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E69" s="25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F69" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G69" s="25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H69" s="25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I69" s="25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J69" s="25" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L69" s="26" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="23" t="inlineStr">
         <is>
-          <t>Effective AEs</t>
+          <t>AEs (new hires)</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C70" s="27" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D70" s="27" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="E70" s="27" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G70" s="27" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="H70" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="I70" s="27" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="J70" s="27" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K70" s="27" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="L70" s="26" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="C70" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
+          <t>Effective AEs</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C71" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D71" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G71" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H71" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I71" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J71" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="K71" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="L71" s="26" t="n">
-        <v>5</v>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C71" s="27" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D71" s="27" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="G71" s="27" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="H71" s="27" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I71" s="27" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J71" s="27" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="K71" s="27" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C72" s="27" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D72" s="27" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="E72" s="27" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="G72" s="27" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="H72" s="27" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="I72" s="27" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="J72" s="27" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="K72" s="27" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="L72" s="26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C72" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D72" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G72" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H72" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="E73" s="27" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="G73" s="27" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H73" s="27" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="I73" s="27" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="J73" s="27" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="23" t="inlineStr">
+        <is>
           <t>Monthly cost</t>
         </is>
       </c>
-      <c r="C73" s="28" t="inlineStr">
-        <is>
-          <t>€6.4k</t>
-        </is>
-      </c>
-      <c r="D73" s="28" t="inlineStr">
-        <is>
-          <t>€8.8k</t>
-        </is>
-      </c>
-      <c r="E73" s="28" t="inlineStr">
-        <is>
-          <t>€17.6k</t>
-        </is>
-      </c>
-      <c r="F73" s="28" t="inlineStr">
-        <is>
-          <t>€27.6k</t>
-        </is>
-      </c>
-      <c r="G73" s="28" t="inlineStr">
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>€5.8k</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr">
+        <is>
+          <t>€8.2k</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>€23.0k</t>
+        </is>
+      </c>
+      <c r="F74" s="28" t="inlineStr">
+        <is>
+          <t>€27.0k</t>
+        </is>
+      </c>
+      <c r="G74" s="28" t="inlineStr">
         <is>
           <t>€37.0k</t>
         </is>
       </c>
-      <c r="H73" s="28" t="inlineStr">
+      <c r="H74" s="28" t="inlineStr">
         <is>
           <t>€37.0k</t>
         </is>
       </c>
-      <c r="I73" s="28" t="inlineStr">
+      <c r="I74" s="28" t="inlineStr">
         <is>
           <t>€41.0k</t>
         </is>
       </c>
-      <c r="J73" s="28" t="inlineStr">
+      <c r="J74" s="28" t="inlineStr">
         <is>
           <t>€47.0k</t>
         </is>
       </c>
-      <c r="K73" s="28" t="inlineStr">
+      <c r="K74" s="28" t="inlineStr">
         <is>
           <t>€47.0k</t>
         </is>
       </c>
-      <c r="L73" s="26" t="inlineStr">
-        <is>
-          <t>€269k total</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="L74" s="26" t="inlineStr">
+        <is>
+          <t>€273k total</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>DEAL FLOW</t>
         </is>
       </c>
-      <c r="B75" s="24" t="inlineStr">
+      <c r="B76" s="24" t="inlineStr">
         <is>
           <t>from AE capacity</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="22" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B76" s="22" t="inlineStr"/>
-      <c r="C76" s="22" t="inlineStr">
+      <c r="B77" s="22" t="inlineStr"/>
+      <c r="C77" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D76" s="22" t="inlineStr">
+      <c r="D77" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E76" s="22" t="inlineStr">
+      <c r="E77" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F76" s="22" t="inlineStr">
+      <c r="F77" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
+      <c r="G77" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H76" s="22" t="inlineStr">
+      <c r="H77" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I76" s="22" t="inlineStr">
+      <c r="I77" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J76" s="22" t="inlineStr">
+      <c r="J77" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K76" s="22" t="inlineStr">
+      <c r="K77" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L76" s="22" t="inlineStr">
+      <c r="L77" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="23" t="inlineStr">
-        <is>
-          <t>Pilots</t>
-        </is>
-      </c>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C77" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D77" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F77" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H77" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="I77" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K77" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="L77" s="26" t="n">
-        <v>46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Pilots</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>€50K ARR</t>
+          <t>€15K ARR</t>
         </is>
       </c>
       <c r="C78" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G78" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H78" s="28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I78" s="28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J78" s="28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K78" s="28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L78" s="26" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>€100K ARR</t>
+          <t>€50K ARR</t>
         </is>
       </c>
       <c r="C79" s="28" t="n">
@@ -4859,862 +4827,809 @@
         <v>1</v>
       </c>
       <c r="G79" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="23" t="inlineStr">
         <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="45" t="inlineStr">
+        <is>
+          <t>1*</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
           <t>Total deals closing</t>
         </is>
       </c>
-      <c r="C80" s="27" t="n">
+      <c r="C81" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D80" s="27" t="n">
+      <c r="E81" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G81" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H81" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I81" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J81" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K81" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>* = deal already in pipeline (not derived from capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>PIPELINE NEEDED</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>2-mo cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr"/>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J85" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K85" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L85" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M85" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>Deals closing</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>when they close</t>
+        </is>
+      </c>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F80" s="27" t="n">
+      <c r="G86" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="G80" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="H80" s="27" t="n">
+      <c r="H86" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I86" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="I80" s="27" t="n">
+      <c r="J86" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K86" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="J80" s="27" t="n">
+      <c r="L86" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="K80" s="27" t="n">
+      <c r="M86" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="L80" s="26" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="22" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B83" s="22" t="inlineStr"/>
-      <c r="C83" s="22" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D83" s="22" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E83" s="22" t="inlineStr">
+      <c r="N86" s="29" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>SQLs needed</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>when to generate</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E87" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="F87" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G87" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="H87" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="I87" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J87" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="K87" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="L87" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="44" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>ARR WATERFALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr"/>
+      <c r="C90" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F83" s="22" t="inlineStr">
+      <c r="D90" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G83" s="22" t="inlineStr">
+      <c r="E90" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H83" s="22" t="inlineStr">
+      <c r="F90" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I83" s="22" t="inlineStr">
+      <c r="G90" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J83" s="22" t="inlineStr">
+      <c r="H90" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K83" s="22" t="inlineStr">
+      <c r="I90" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L83" s="22" t="inlineStr">
+      <c r="J90" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M83" s="22" t="inlineStr">
+      <c r="K90" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N83" s="22" t="inlineStr">
+      <c r="L90" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="23" t="inlineStr">
-        <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C84" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G84" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="H84" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I84" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="J84" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="L84" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="M84" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="N84" s="29" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="23" t="inlineStr">
-        <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B85" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C85" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="D85" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E85" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="F85" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G85" s="43" t="n">
-        <v>80</v>
-      </c>
-      <c r="H85" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="I85" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="J85" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="K85" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="L85" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="44" t="n">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B88" s="22" t="inlineStr"/>
-      <c r="C88" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D88" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E88" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F88" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G88" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H88" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I88" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J88" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K88" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L88" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C89" s="30" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D89" s="30" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="E89" s="30" t="inlineStr">
-        <is>
-          <t>€195k</t>
-        </is>
-      </c>
-      <c r="F89" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="G89" s="30" t="inlineStr">
-        <is>
-          <t>€240k</t>
-        </is>
-      </c>
-      <c r="H89" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="I89" s="30" t="inlineStr">
-        <is>
-          <t>€305k</t>
-        </is>
-      </c>
-      <c r="J89" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="K89" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="L89" s="29" t="inlineStr">
-        <is>
-          <t>€1.94M</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B90" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C90" s="31" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D90" s="31" t="inlineStr">
-        <is>
-          <t>€60k</t>
-        </is>
-      </c>
-      <c r="E90" s="31" t="inlineStr">
-        <is>
-          <t>€255k</t>
-        </is>
-      </c>
-      <c r="F90" s="31" t="inlineStr">
-        <is>
-          <t>€465k</t>
-        </is>
-      </c>
-      <c r="G90" s="31" t="inlineStr">
-        <is>
-          <t>€705k</t>
-        </is>
-      </c>
-      <c r="H90" s="31" t="inlineStr">
-        <is>
-          <t>€995k</t>
-        </is>
-      </c>
-      <c r="I90" s="31" t="inlineStr">
-        <is>
-          <t>€1.30M</t>
-        </is>
-      </c>
-      <c r="J90" s="31" t="inlineStr">
-        <is>
-          <t>€1.62M</t>
-        </is>
-      </c>
-      <c r="K90" s="31" t="inlineStr">
-        <is>
-          <t>€1.94M</t>
-        </is>
-      </c>
-      <c r="L90" s="32" t="inlineStr">
-        <is>
-          <t>€1.94M</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B91" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C91" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="I91" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="J91" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="K91" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="L91" s="42" t="inlineStr">
-        <is>
-          <t>+€175k</t>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C91" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D91" s="30" t="inlineStr">
+        <is>
+          <t>€115k</t>
+        </is>
+      </c>
+      <c r="E91" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="G91" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="H91" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="I91" s="30" t="inlineStr">
+        <is>
+          <t>€305k</t>
+        </is>
+      </c>
+      <c r="J91" s="30" t="inlineStr">
+        <is>
+          <t>€320k</t>
+        </is>
+      </c>
+      <c r="K91" s="30" t="inlineStr">
+        <is>
+          <t>€320k</t>
+        </is>
+      </c>
+      <c r="L91" s="29" t="inlineStr">
+        <is>
+          <t>€2.08M</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="23" t="inlineStr">
         <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B92" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C92" s="38" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D92" s="38" t="inlineStr">
+        <is>
+          <t>€130k</t>
+        </is>
+      </c>
+      <c r="E92" s="38" t="inlineStr">
+        <is>
+          <t>€340k</t>
+        </is>
+      </c>
+      <c r="F92" s="38" t="inlineStr">
+        <is>
+          <t>€550k</t>
+        </is>
+      </c>
+      <c r="G92" s="38" t="inlineStr">
+        <is>
+          <t>€840k</t>
+        </is>
+      </c>
+      <c r="H92" s="38" t="inlineStr">
+        <is>
+          <t>€1.13M</t>
+        </is>
+      </c>
+      <c r="I92" s="38" t="inlineStr">
+        <is>
+          <t>€1.44M</t>
+        </is>
+      </c>
+      <c r="J92" s="38" t="inlineStr">
+        <is>
+          <t>€1.75M</t>
+        </is>
+      </c>
+      <c r="K92" s="38" t="inlineStr">
+        <is>
+          <t>€2.08M</t>
+        </is>
+      </c>
+      <c r="L92" s="41" t="inlineStr">
+        <is>
+          <t>€2.08M</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>upside</t>
+        </is>
+      </c>
+      <c r="C93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="K93" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="L93" s="42" t="inlineStr">
+        <is>
+          <t>+€140k</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C92" s="35" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D92" s="35" t="inlineStr">
-        <is>
-          <t>€60k</t>
-        </is>
-      </c>
-      <c r="E92" s="35" t="inlineStr">
-        <is>
-          <t>€255k</t>
-        </is>
-      </c>
-      <c r="F92" s="35" t="inlineStr">
-        <is>
-          <t>€465k</t>
-        </is>
-      </c>
-      <c r="G92" s="35" t="inlineStr">
-        <is>
-          <t>€705k</t>
-        </is>
-      </c>
-      <c r="H92" s="35" t="inlineStr">
-        <is>
-          <t>€1.03M</t>
-        </is>
-      </c>
-      <c r="I92" s="35" t="inlineStr">
-        <is>
-          <t>€1.37M</t>
-        </is>
-      </c>
-      <c r="J92" s="35" t="inlineStr">
-        <is>
-          <t>€1.73M</t>
-        </is>
-      </c>
-      <c r="K92" s="35" t="inlineStr">
-        <is>
-          <t>€2.12M</t>
-        </is>
-      </c>
-      <c r="L92" s="36" t="inlineStr">
-        <is>
-          <t>€2.12M</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="20" t="inlineStr">
+      <c r="C94" s="35" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D94" s="35" t="inlineStr">
+        <is>
+          <t>€130k</t>
+        </is>
+      </c>
+      <c r="E94" s="35" t="inlineStr">
+        <is>
+          <t>€340k</t>
+        </is>
+      </c>
+      <c r="F94" s="35" t="inlineStr">
+        <is>
+          <t>€550k</t>
+        </is>
+      </c>
+      <c r="G94" s="35" t="inlineStr">
+        <is>
+          <t>€840k</t>
+        </is>
+      </c>
+      <c r="H94" s="35" t="inlineStr">
+        <is>
+          <t>€1.13M</t>
+        </is>
+      </c>
+      <c r="I94" s="35" t="inlineStr">
+        <is>
+          <t>€1.44M</t>
+        </is>
+      </c>
+      <c r="J94" s="35" t="inlineStr">
+        <is>
+          <t>€1.82M</t>
+        </is>
+      </c>
+      <c r="K94" s="35" t="inlineStr">
+        <is>
+          <t>€2.21M</t>
+        </is>
+      </c>
+      <c r="L94" s="36" t="inlineStr">
+        <is>
+          <t>€2.21M</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="18" t="inlineStr">
-        <is>
-          <t>64 deals ÷ 10% = 640 meetings needed over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="18">
-        <f> 72 meetings/month − 15 from SMB BDRs = 57 from dedicated BDRs</f>
-        <v/>
-      </c>
-    </row>
     <row r="97">
-      <c r="A97" s="37" t="inlineStr">
-        <is>
-          <t>57/mo ÷ 15/BDR = 4 dedicated MM BDRs needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>65 deals ÷ 10% = 650 meetings over 9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="18">
+        <f> 73/mo − 15 from SMB BDRs = 58 from dedicated BDRs</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="37" t="inlineStr">
+        <is>
+          <t>58/mo ÷ 15/BDR = 4 dedicated MM BDRs needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 3: HYPER-PUSH</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="19" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>Build the €3M machine — staff it like a proven motion</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>NARRATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="inlineStr">
-        <is>
-          <t>Maximum conviction. Victor goes full-time in May (one month early). First new AE in June, two more in July, two more in September, another in November. Martijn shifts to 0.5 FTE in August. BDR team scales to 6 by Q4. Combined with SMB spillover, we're generating 115+ MM meetings/month by October.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="inlineStr">
-        <is>
-          <t>This requires an MM team lead by August — someone who can run pipeline reviews, maintain process quality across 7+ AEs, and own the weekly forecast. Without that hire, AE variance will kill the model. We also need solutioning capacity for 3+ large deals in parallel by Q4.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="21" t="inlineStr">
         <is>
-          <t>Risk profile: HIGH. Monthly burn hits €62K by December. Total 9-month cost: €384K. But the output is €3.2M new deal ARR + €330K expansion = €3.5M total. That's a 9x return on the hiring investment and puts MM on track for a €5M+ run-rate entering 2027.</t>
+          <t>Maximum conviction. Victor goes full-time in May (one month early). The May large deal anchors Q2 at €100K+. First new AE in June, two more in July, two more in September, another in November. Martijn stays at 0.5 FTE throughout. BDR team scales to 6 by Q4. Combined with SMB spillover, we're generating 115+ MM meetings/month by October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="inlineStr">
+        <is>
+          <t>This requires an MM team lead by August — someone who can run pipeline reviews, maintain process quality across 7+ AEs, and own the weekly forecast. Without that hire, AE variance will kill the model. We also need solutioning capacity for 3+ large deals in parallel by Q4.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="inlineStr">
+      <c r="A108" s="21" t="inlineStr">
+        <is>
+          <t>Risk profile: HIGH. Monthly burn hits €62K by December. Total 9-month cost: ~€385K. But the output targets €3.3M new deal ARR + expansion. That's a 9x return on the hiring investment and puts MM on track for a €5M+ run-rate entering 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
         <is>
           <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="22" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="22" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B109" s="22" t="inlineStr">
+      <c r="B111" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C109" s="22" t="inlineStr">
+      <c r="C111" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr">
+      <c r="D111" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E109" s="22" t="inlineStr">
+      <c r="E111" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F109" s="22" t="inlineStr">
+      <c r="F111" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G109" s="22" t="inlineStr">
+      <c r="G111" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H109" s="22" t="inlineStr">
+      <c r="H111" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I109" s="22" t="inlineStr">
+      <c r="I111" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J109" s="22" t="inlineStr">
+      <c r="J111" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K109" s="22" t="inlineStr">
+      <c r="K111" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L109" s="22" t="inlineStr">
+      <c r="L111" s="22" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B110" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C110" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D110" s="25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E110" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F110" s="25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G110" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H110" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I110" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J110" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K110" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L110" s="26" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="23" t="inlineStr">
-        <is>
-          <t>AEs (new hires)</t>
-        </is>
-      </c>
-      <c r="B111" s="24" t="inlineStr">
-        <is>
-          <t>cumulative</t>
-        </is>
-      </c>
-      <c r="C111" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G111" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H111" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I111" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J111" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K111" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L111" s="26" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="23" t="inlineStr">
         <is>
-          <t>Effective AEs</t>
+          <t>AEs (ramped)</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C112" s="27" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D112" s="27" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="E112" s="27" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="F112" s="27" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="G112" s="27" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H112" s="27" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="I112" s="27" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="J112" s="27" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="K112" s="27" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="L112" s="26" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C112" s="25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K112" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
+          <t>AEs (new hires)</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>cumulative</t>
         </is>
       </c>
       <c r="C113" s="25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D113" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="25" t="n">
         <v>1</v>
-      </c>
-      <c r="E113" s="25" t="n">
-        <v>2</v>
       </c>
       <c r="F113" s="25" t="n">
         <v>3</v>
       </c>
       <c r="G113" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H113" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I113" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J113" s="25" t="n">
         <v>6</v>
@@ -5729,880 +5644,994 @@
     <row r="114">
       <c r="A114" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
+          <t>Effective AEs</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>incl. ramp</t>
         </is>
       </c>
       <c r="C114" s="27" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D114" s="27" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="F114" s="27" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="G114" s="27" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="H114" s="27" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I114" s="27" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="J114" s="27" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="K114" s="27" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="L114" s="26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7.2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="23" t="inlineStr">
         <is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C115" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D115" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G115" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I115" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J115" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K115" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L115" s="26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="23" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C116" s="27" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D116" s="27" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E116" s="27" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="F116" s="27" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="G116" s="27" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="H116" s="27" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="I116" s="27" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="J116" s="27" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="K116" s="27" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="L116" s="26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="23" t="inlineStr">
+        <is>
           <t>Monthly cost</t>
         </is>
       </c>
-      <c r="C115" s="28" t="inlineStr">
-        <is>
-          <t>€6.4k</t>
-        </is>
-      </c>
-      <c r="D115" s="28" t="inlineStr">
-        <is>
-          <t>€11.2k</t>
-        </is>
-      </c>
-      <c r="E115" s="28" t="inlineStr">
-        <is>
-          <t>€23.6k</t>
-        </is>
-      </c>
-      <c r="F115" s="28" t="inlineStr">
-        <is>
-          <t>€39.6k</t>
-        </is>
-      </c>
-      <c r="G115" s="28" t="inlineStr">
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>€5.8k</t>
+        </is>
+      </c>
+      <c r="D117" s="28" t="inlineStr">
+        <is>
+          <t>€13.0k</t>
+        </is>
+      </c>
+      <c r="E117" s="28" t="inlineStr">
+        <is>
+          <t>€23.0k</t>
+        </is>
+      </c>
+      <c r="F117" s="28" t="inlineStr">
+        <is>
+          <t>€39.0k</t>
+        </is>
+      </c>
+      <c r="G117" s="28" t="inlineStr">
         <is>
           <t>€43.0k</t>
         </is>
       </c>
-      <c r="H115" s="28" t="inlineStr">
+      <c r="H117" s="28" t="inlineStr">
         <is>
           <t>€59.0k</t>
         </is>
       </c>
-      <c r="I115" s="28" t="inlineStr">
+      <c r="I117" s="28" t="inlineStr">
         <is>
           <t>€63.0k</t>
         </is>
       </c>
-      <c r="J115" s="28" t="inlineStr">
+      <c r="J117" s="28" t="inlineStr">
         <is>
           <t>€69.0k</t>
         </is>
       </c>
-      <c r="K115" s="28" t="inlineStr">
+      <c r="K117" s="28" t="inlineStr">
         <is>
           <t>€69.0k</t>
         </is>
       </c>
-      <c r="L115" s="26" t="inlineStr">
+      <c r="L117" s="26" t="inlineStr">
         <is>
           <t>€384k total</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>DEAL FLOW</t>
         </is>
       </c>
-      <c r="B117" s="24" t="inlineStr">
+      <c r="B119" s="24" t="inlineStr">
         <is>
           <t>from AE capacity</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="22" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B118" s="22" t="inlineStr"/>
-      <c r="C118" s="22" t="inlineStr">
+      <c r="B120" s="22" t="inlineStr"/>
+      <c r="C120" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D118" s="22" t="inlineStr">
+      <c r="D120" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E118" s="22" t="inlineStr">
+      <c r="E120" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F118" s="22" t="inlineStr">
+      <c r="F120" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G118" s="22" t="inlineStr">
+      <c r="G120" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H118" s="22" t="inlineStr">
+      <c r="H120" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I118" s="22" t="inlineStr">
+      <c r="I120" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J118" s="22" t="inlineStr">
+      <c r="J120" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K118" s="22" t="inlineStr">
+      <c r="K120" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L118" s="22" t="inlineStr">
+      <c r="L120" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="23" t="inlineStr">
-        <is>
-          <t>Pilots</t>
-        </is>
-      </c>
-      <c r="B119" s="24" t="inlineStr">
-        <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C119" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D119" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F119" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="G119" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="H119" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="I119" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="J119" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="K119" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="L119" s="26" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B120" s="24" t="inlineStr">
-        <is>
-          <t>€50K ARR</t>
-        </is>
-      </c>
-      <c r="C120" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G120" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H120" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I120" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="K120" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L120" s="26" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Pilots</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>€100K ARR</t>
+          <t>€15K ARR</t>
         </is>
       </c>
       <c r="C121" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" s="28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E121" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F121" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G121" s="28" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H121" s="28" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I121" s="28" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J121" s="28" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K121" s="28" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L121" s="26" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="23" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>€50K ARR</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I122" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J122" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K122" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L122" s="26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="23" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="45" t="inlineStr">
+        <is>
+          <t>1*</t>
+        </is>
+      </c>
+      <c r="E123" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K123" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L123" s="26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="23" t="inlineStr">
+        <is>
           <t>Total deals closing</t>
         </is>
       </c>
-      <c r="C122" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D122" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" s="27" t="n">
+      <c r="C124" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F122" s="27" t="n">
+      <c r="F124" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G124" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H124" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="I124" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="J124" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="K124" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="L124" s="26" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="24" t="inlineStr">
+        <is>
+          <t>* = deal already in pipeline (not derived from capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>PIPELINE NEEDED</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>2-mo cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B128" s="22" t="inlineStr"/>
+      <c r="C128" s="22" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G128" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I128" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J128" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K128" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L128" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M128" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N128" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="23" t="inlineStr">
+        <is>
+          <t>Deals closing</t>
+        </is>
+      </c>
+      <c r="B129" s="24" t="inlineStr">
+        <is>
+          <t>when they close</t>
+        </is>
+      </c>
+      <c r="C129" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D129" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E129" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G129" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H129" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="I129" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="J129" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K129" s="30" t="n">
+        <v>17</v>
+      </c>
+      <c r="L129" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="M129" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="N129" s="29" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="23" t="inlineStr">
+        <is>
+          <t>SQLs needed</t>
+        </is>
+      </c>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
+          <t>when to generate</t>
+        </is>
+      </c>
+      <c r="C130" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="G122" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="H122" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="I122" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="J122" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="K122" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="L122" s="26" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B124" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="22" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B125" s="22" t="inlineStr"/>
-      <c r="C125" s="22" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D125" s="22" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E125" s="22" t="inlineStr">
+      <c r="D130" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E130" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="F130" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G130" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="H130" s="43" t="n">
+        <v>160</v>
+      </c>
+      <c r="I130" s="43" t="n">
+        <v>170</v>
+      </c>
+      <c r="J130" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="K130" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="L130" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="44" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>ARR WATERFALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B133" s="22" t="inlineStr"/>
+      <c r="C133" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F125" s="22" t="inlineStr">
+      <c r="D133" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G125" s="22" t="inlineStr">
+      <c r="E133" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H125" s="22" t="inlineStr">
+      <c r="F133" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I125" s="22" t="inlineStr">
+      <c r="G133" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J125" s="22" t="inlineStr">
+      <c r="H133" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K125" s="22" t="inlineStr">
+      <c r="I133" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L125" s="22" t="inlineStr">
+      <c r="J133" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M125" s="22" t="inlineStr">
+      <c r="K133" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N125" s="22" t="inlineStr">
+      <c r="L133" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="23" t="inlineStr">
-        <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B126" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C126" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F126" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H126" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="I126" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="J126" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="K126" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="L126" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="M126" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N126" s="29" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="23" t="inlineStr">
-        <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C127" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="D127" s="43" t="n">
-        <v>30</v>
-      </c>
-      <c r="E127" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F127" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="G127" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="H127" s="43" t="n">
-        <v>160</v>
-      </c>
-      <c r="I127" s="43" t="n">
-        <v>170</v>
-      </c>
-      <c r="J127" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="K127" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="L127" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="44" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B130" s="22" t="inlineStr"/>
-      <c r="C130" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D130" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E130" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F130" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G130" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H130" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I130" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J130" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K130" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L130" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C131" s="30" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D131" s="30" t="inlineStr">
-        <is>
-          <t>€80k</t>
-        </is>
-      </c>
-      <c r="E131" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="F131" s="30" t="inlineStr">
-        <is>
-          <t>€305k</t>
-        </is>
-      </c>
-      <c r="G131" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="H131" s="30" t="inlineStr">
-        <is>
-          <t>€515k</t>
-        </is>
-      </c>
-      <c r="I131" s="30" t="inlineStr">
-        <is>
-          <t>€530k</t>
-        </is>
-      </c>
-      <c r="J131" s="30" t="inlineStr">
-        <is>
-          <t>€610k</t>
-        </is>
-      </c>
-      <c r="K131" s="30" t="inlineStr">
-        <is>
-          <t>€610k</t>
-        </is>
-      </c>
-      <c r="L131" s="29" t="inlineStr">
-        <is>
-          <t>€3.21M</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B132" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C132" s="38" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D132" s="38" t="inlineStr">
-        <is>
-          <t>€110k</t>
-        </is>
-      </c>
-      <c r="E132" s="38" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="F132" s="38" t="inlineStr">
-        <is>
-          <t>€625k</t>
-        </is>
-      </c>
-      <c r="G132" s="38" t="inlineStr">
-        <is>
-          <t>€945k</t>
-        </is>
-      </c>
-      <c r="H132" s="38" t="inlineStr">
-        <is>
-          <t>€1.46M</t>
-        </is>
-      </c>
-      <c r="I132" s="38" t="inlineStr">
-        <is>
-          <t>€1.99M</t>
-        </is>
-      </c>
-      <c r="J132" s="38" t="inlineStr">
-        <is>
-          <t>€2.60M</t>
-        </is>
-      </c>
-      <c r="K132" s="38" t="inlineStr">
-        <is>
-          <t>€3.21M</t>
-        </is>
-      </c>
-      <c r="L132" s="41" t="inlineStr">
-        <is>
-          <t>€3.21M</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="23" t="inlineStr">
-        <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B133" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C133" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="I133" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="J133" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="K133" s="34" t="inlineStr">
-        <is>
-          <t>€190k</t>
-        </is>
-      </c>
-      <c r="L133" s="42" t="inlineStr">
-        <is>
-          <t>+€330k</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="23" t="inlineStr">
         <is>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D134" s="30" t="inlineStr">
+        <is>
+          <t>€195k</t>
+        </is>
+      </c>
+      <c r="E134" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="G134" s="30" t="inlineStr">
+        <is>
+          <t>€320k</t>
+        </is>
+      </c>
+      <c r="H134" s="30" t="inlineStr">
+        <is>
+          <t>€515k</t>
+        </is>
+      </c>
+      <c r="I134" s="30" t="inlineStr">
+        <is>
+          <t>€530k</t>
+        </is>
+      </c>
+      <c r="J134" s="30" t="inlineStr">
+        <is>
+          <t>€610k</t>
+        </is>
+      </c>
+      <c r="K134" s="30" t="inlineStr">
+        <is>
+          <t>€610k</t>
+        </is>
+      </c>
+      <c r="L134" s="29" t="inlineStr">
+        <is>
+          <t>€3.29M</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="23" t="inlineStr">
+        <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B135" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C135" s="38" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D135" s="38" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="E135" s="38" t="inlineStr">
+        <is>
+          <t>€420k</t>
+        </is>
+      </c>
+      <c r="F135" s="38" t="inlineStr">
+        <is>
+          <t>€710k</t>
+        </is>
+      </c>
+      <c r="G135" s="38" t="inlineStr">
+        <is>
+          <t>€1.03M</t>
+        </is>
+      </c>
+      <c r="H135" s="38" t="inlineStr">
+        <is>
+          <t>€1.54M</t>
+        </is>
+      </c>
+      <c r="I135" s="38" t="inlineStr">
+        <is>
+          <t>€2.08M</t>
+        </is>
+      </c>
+      <c r="J135" s="38" t="inlineStr">
+        <is>
+          <t>€2.69M</t>
+        </is>
+      </c>
+      <c r="K135" s="38" t="inlineStr">
+        <is>
+          <t>€3.29M</t>
+        </is>
+      </c>
+      <c r="L135" s="41" t="inlineStr">
+        <is>
+          <t>€3.29M</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B136" s="24" t="inlineStr">
+        <is>
+          <t>upside</t>
+        </is>
+      </c>
+      <c r="C136" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D136" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="34" t="inlineStr">
+        <is>
+          <t>€35k</t>
+        </is>
+      </c>
+      <c r="J136" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="K136" s="34" t="inlineStr">
+        <is>
+          <t>€155k</t>
+        </is>
+      </c>
+      <c r="L136" s="42" t="inlineStr">
+        <is>
+          <t>+€260k</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C134" s="35" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="D134" s="35" t="inlineStr">
-        <is>
-          <t>€110k</t>
-        </is>
-      </c>
-      <c r="E134" s="35" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="F134" s="35" t="inlineStr">
-        <is>
-          <t>€625k</t>
-        </is>
-      </c>
-      <c r="G134" s="35" t="inlineStr">
-        <is>
-          <t>€945k</t>
-        </is>
-      </c>
-      <c r="H134" s="35" t="inlineStr">
-        <is>
-          <t>€1.50M</t>
-        </is>
-      </c>
-      <c r="I134" s="35" t="inlineStr">
-        <is>
-          <t>€2.06M</t>
-        </is>
-      </c>
-      <c r="J134" s="35" t="inlineStr">
-        <is>
-          <t>€2.74M</t>
-        </is>
-      </c>
-      <c r="K134" s="35" t="inlineStr">
-        <is>
-          <t>€3.54M</t>
-        </is>
-      </c>
-      <c r="L134" s="36" t="inlineStr">
-        <is>
-          <t>€3.54M</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="20" t="inlineStr">
+      <c r="C137" s="35" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D137" s="35" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="E137" s="35" t="inlineStr">
+        <is>
+          <t>€420k</t>
+        </is>
+      </c>
+      <c r="F137" s="35" t="inlineStr">
+        <is>
+          <t>€710k</t>
+        </is>
+      </c>
+      <c r="G137" s="35" t="inlineStr">
+        <is>
+          <t>€1.03M</t>
+        </is>
+      </c>
+      <c r="H137" s="35" t="inlineStr">
+        <is>
+          <t>€1.54M</t>
+        </is>
+      </c>
+      <c r="I137" s="35" t="inlineStr">
+        <is>
+          <t>€2.11M</t>
+        </is>
+      </c>
+      <c r="J137" s="35" t="inlineStr">
+        <is>
+          <t>€2.79M</t>
+        </is>
+      </c>
+      <c r="K137" s="35" t="inlineStr">
+        <is>
+          <t>€3.56M</t>
+        </is>
+      </c>
+      <c r="L137" s="36" t="inlineStr">
+        <is>
+          <t>€3.56M</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
         <is>
           <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="18" t="inlineStr">
-        <is>
-          <t>105 deals ÷ 10% = 1050 meetings needed over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="18">
-        <f> 117 meetings/month − 15 from SMB BDRs = 102 from dedicated BDRs</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="37" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>105 deals ÷ 10% = 1050 meetings over 9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="18">
+        <f> 117/mo − 15 from SMB BDRs = 102 from dedicated BDRs</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="37" t="inlineStr">
         <is>
           <t>102/mo ÷ 15/BDR = 7 dedicated MM BDRs needed</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A64:K64"/>
     <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A107:K107"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A108:K108"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A104:K104"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A106:K106"/>
     <mergeCell ref="A8:K8"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A13:K13"/>

--- a/work/WP_SEO_AI_Scenario_Planning.xlsx
+++ b/work/WP_SEO_AI_Scenario_Planning.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -139,6 +139,18 @@
       <color rgb="00F5A623"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B748FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B748FF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -226,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -317,6 +329,8 @@
     <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3011,11 +3025,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N142"/>
+  <dimension ref="A1:N150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -3066,3116 +3080,2923 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>New AE ramp: 50% → 75% → 100% over 3 months. Ramped AEs (Martijn, Victor) produce at full capacity.</t>
+          <t>New AE ramp: 50% → 75% → 100% over 3 months. Existing AEs (incl. SMB→MM switch) = no ramp.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Martijn: max 0.5 FTE throughout. Victor: 0.2 FTE → 1.0 FTE (Jun for baseline/push, May for hyper-push).</t>
+          <t>Martijn: 0.2 FTE Apr-Jul, 0.5 FTE Aug+. Mossel: 0.2 FTE throughout. Victor: 0.2→1.0 FTE.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Blended close rate: 10% (meeting → deal). Deal type determined during sales process.</t>
+          <t>Optional lever: switch 1 SMB AE to MM (no ramp needed). Decision point: end of July.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>SMB BDR team contributes ~15 MM meetings/month (free pipeline).</t>
+          <t>Blended close rate: 10% (meeting → deal). Deal type determined during sales process.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>Deal cycle: 2 months (SQL → close). Pipeline row shows when SQLs must be generated.</t>
+          <t>SMB BDR team contributes ~15 MM meetings/month (free pipeline).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Pilot conversion at month 5: 40% → Medium, 10% → Large. Expansion = upside, not counted toward €2M.</t>
+          <t>Deal cycle: 2 months (SQL → close). Pipeline row shows when SQLs must be generated.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>AE cost: €6K/mo. BDR cost: €4K/mo.</t>
+          <t>Pilot conversion at month 5: 40% → Medium, 10% → Large. Expansion = upside, not counted toward €2M.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Push/Hyper scenarios include 1 large deal closing in May (currently in advanced pipeline).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+          <t>AE cost: €6K/mo. BDR cost: €4K/mo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Push scenario includes 1 large deal closing in May (currently in advanced pipeline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 1: BASELINE</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Conservative ramp — prove the motion, then scale</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>NARRATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>We start with 0.7 FTE AE capacity (Martijn 0.5 + Victor 0.2) and 0.4 FTE BDR. Victor goes full-time in June, giving us 1.5 effective AEs. One new AE joins in July, ramping through Q3. A second new hire follows in October. BDR scales to 3 by Q4, supplemented by ~15 MM meetings/month from the SMB BDR team.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>This is the 'prove it before you scale' path. We close our first pilots in May-June, get the narrative tested in 20+ meetings before hiring aggressively, and let the month-5 pilot reviews (starting September) validate the conversion thesis. If pilot conversion lands at 40%+, we have the signal to accelerate into 2027.</t>
+          <t>We start with 0.6 FTE AE capacity (Martijn 0.2 + Mossel 0.2 + Victor 0.2) and 0.4 FTE BDR. Victor goes full-time in June, giving us 1.4 effective AEs. Martijn increases to 0.5 FTE in August. One new AE joins in July, a second in October. BDR scales to 3 by Q4, supplemented by ~15 MM meetings/month from the SMB BDR team.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>Risk profile: LOW. Total cost under €185K over 9 months. Downside: we land around €1.6M — short of €2M but with a clean foundation and proven playbook. Expansion from pilot conversions adds upside. The gap tells us exactly how much to accelerate in Q1 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+          <t>This is the 'prove it before you scale' path. We close our first pilots in May-June, get the narrative tested in 20+ meetings, and let the month-5 pilot reviews (starting September) validate the conversion thesis before committing to more headcount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Risk profile: LOW. Total cost under €185K. Downside: ~€1.6M new deal ARR — short of €2M but with a proven playbook and clear signal on what to accelerate in Q1 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Ramped: Martijn 0.2→0.5 (Aug), Mossel 0.2, Victor 0.2→1.0 (Jun)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J26" s="22" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K26" s="22" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L26" s="22" t="inlineStr">
+      <c r="L28" s="22" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C27" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D27" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K27" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L27" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>AEs (new hires)</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>cumulative</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="26" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>Effective AEs</t>
+          <t>AEs (ramped)</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="G29" s="27" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="I29" s="27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J29" s="27" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="K29" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
+          <t>no ramp</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D29" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F29" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H29" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I29" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J29" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K29" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
+          <t>AEs (new hires)</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>with ramp</t>
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="25" t="n">
+      <c r="K30" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="25" t="n">
-        <v>3</v>
-      </c>
       <c r="L30" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
+          <t>Effective AEs</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>incl. ramp</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="inlineStr">
+        <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="F31" s="27" t="inlineStr">
+      <c r="H31" s="27" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I31" s="27" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="J31" s="27" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="K31" s="27" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="G31" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="K31" s="27" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
       <c r="L31" s="26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3.5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="G33" s="27" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="I33" s="27" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="J33" s="27" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="K33" s="27" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
           <t>Monthly cost</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>€5.8k</t>
-        </is>
-      </c>
-      <c r="D32" s="28" t="inlineStr">
-        <is>
-          <t>€5.8k</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>€13.0k</t>
-        </is>
-      </c>
-      <c r="F32" s="28" t="inlineStr">
-        <is>
-          <t>€19.0k</t>
-        </is>
-      </c>
-      <c r="G32" s="28" t="inlineStr">
-        <is>
-          <t>€23.0k</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="inlineStr">
-        <is>
-          <t>€23.0k</t>
-        </is>
-      </c>
-      <c r="I32" s="28" t="inlineStr">
-        <is>
-          <t>€27.0k</t>
-        </is>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
-        <is>
-          <t>€33.0k</t>
-        </is>
-      </c>
-      <c r="K32" s="28" t="inlineStr">
-        <is>
-          <t>€33.0k</t>
-        </is>
-      </c>
-      <c r="L32" s="26" t="inlineStr">
-        <is>
-          <t>€183k total</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>€5.2k</t>
+        </is>
+      </c>
+      <c r="D34" s="28" t="inlineStr">
+        <is>
+          <t>€5.2k</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
+        <is>
+          <t>€12.4k</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>€18.4k</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="inlineStr">
+        <is>
+          <t>€24.2k</t>
+        </is>
+      </c>
+      <c r="H34" s="28" t="inlineStr">
+        <is>
+          <t>€24.2k</t>
+        </is>
+      </c>
+      <c r="I34" s="28" t="inlineStr">
+        <is>
+          <t>€28.2k</t>
+        </is>
+      </c>
+      <c r="J34" s="28" t="inlineStr">
+        <is>
+          <t>€34.2k</t>
+        </is>
+      </c>
+      <c r="K34" s="28" t="inlineStr">
+        <is>
+          <t>€34.2k</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>€186k total</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>DEAL FLOW</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>from AE capacity</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr"/>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr"/>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L35" s="22" t="inlineStr">
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Pilots</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C36" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="K36" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>€50K ARR</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="26" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Pilots</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>€100K ARR</t>
+          <t>€15K ARR</t>
         </is>
       </c>
       <c r="C38" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F38" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G38" s="28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H38" s="28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J38" s="28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L38" s="26" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>€50K ARR</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C40" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
           <t>Total deals closing</t>
         </is>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C41" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="27" t="n">
+      <c r="D41" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E41" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="27" t="n">
+      <c r="F41" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G41" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>PIPELINE NEEDED</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2-mo cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr"/>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M44" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N44" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>Deals closing</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>when they close</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="I45" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="I39" s="27" t="n">
+      <c r="J45" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="J39" s="27" t="n">
+      <c r="K45" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L45" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="K39" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="L39" s="26" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="inlineStr"/>
-      <c r="C42" s="22" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="M45" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="N45" s="29" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>SQLs needed</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>when to generate</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="F46" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G46" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="H46" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="I46" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="J46" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="K46" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="L46" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M46" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="44" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>ARR WATERFALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr"/>
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="D49" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="E49" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="F49" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="G49" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J42" s="22" t="inlineStr">
+      <c r="H49" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K42" s="22" t="inlineStr">
+      <c r="I49" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L42" s="22" t="inlineStr">
+      <c r="J49" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M42" s="22" t="inlineStr">
+      <c r="K49" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N42" s="22" t="inlineStr">
+      <c r="L49" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C43" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L43" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="M43" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="N43" s="29" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C44" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D44" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="F44" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="H44" s="43" t="n">
-        <v>70</v>
-      </c>
-      <c r="I44" s="43" t="n">
-        <v>70</v>
-      </c>
-      <c r="J44" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="K44" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="L44" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M44" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N44" s="44" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B47" s="22" t="inlineStr"/>
-      <c r="C47" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F47" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G47" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H47" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I47" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J47" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K47" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L47" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C48" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D48" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="E48" s="30" t="inlineStr">
-        <is>
-          <t>€95k</t>
-        </is>
-      </c>
-      <c r="F48" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="G48" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="H48" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="I48" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="J48" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="K48" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="L48" s="29" t="inlineStr">
-        <is>
-          <t>€1.57M</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B49" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D49" s="31" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
-        <is>
-          <t>€125k</t>
-        </is>
-      </c>
-      <c r="F49" s="31" t="inlineStr">
-        <is>
-          <t>€335k</t>
-        </is>
-      </c>
-      <c r="G49" s="31" t="inlineStr">
-        <is>
-          <t>€545k</t>
-        </is>
-      </c>
-      <c r="H49" s="31" t="inlineStr">
-        <is>
-          <t>€770k</t>
-        </is>
-      </c>
-      <c r="I49" s="31" t="inlineStr">
-        <is>
-          <t>€995k</t>
-        </is>
-      </c>
-      <c r="J49" s="31" t="inlineStr">
-        <is>
-          <t>€1.28M</t>
-        </is>
-      </c>
-      <c r="K49" s="31" t="inlineStr">
-        <is>
-          <t>€1.57M</t>
-        </is>
-      </c>
-      <c r="L49" s="32" t="inlineStr">
-        <is>
-          <t>€1.57M</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="K50" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="L50" s="42" t="inlineStr">
-        <is>
-          <t>+€105k</t>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>€95k</t>
+        </is>
+      </c>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <t>€225k</t>
+        </is>
+      </c>
+      <c r="H50" s="30" t="inlineStr">
+        <is>
+          <t>€225k</t>
+        </is>
+      </c>
+      <c r="I50" s="30" t="inlineStr">
+        <is>
+          <t>€225k</t>
+        </is>
+      </c>
+      <c r="J50" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="K50" s="30" t="inlineStr">
+        <is>
+          <t>€305k</t>
+        </is>
+      </c>
+      <c r="L50" s="29" t="inlineStr">
+        <is>
+          <t>€1.60M</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B51" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>€30k</t>
+        </is>
+      </c>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>€125k</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr">
+        <is>
+          <t>€335k</t>
+        </is>
+      </c>
+      <c r="G51" s="31" t="inlineStr">
+        <is>
+          <t>€560k</t>
+        </is>
+      </c>
+      <c r="H51" s="31" t="inlineStr">
+        <is>
+          <t>€785k</t>
+        </is>
+      </c>
+      <c r="I51" s="31" t="inlineStr">
+        <is>
+          <t>€1.01M</t>
+        </is>
+      </c>
+      <c r="J51" s="31" t="inlineStr">
+        <is>
+          <t>€1.30M</t>
+        </is>
+      </c>
+      <c r="K51" s="31" t="inlineStr">
+        <is>
+          <t>€1.60M</t>
+        </is>
+      </c>
+      <c r="L51" s="32" t="inlineStr">
+        <is>
+          <t>€1.60M</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>upside</t>
+        </is>
+      </c>
+      <c r="C52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="34" t="inlineStr">
+        <is>
+          <t>€35k</t>
+        </is>
+      </c>
+      <c r="K52" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="L52" s="42" t="inlineStr">
+        <is>
+          <t>+€105k</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C51" s="35" t="inlineStr">
+      <c r="C53" s="35" t="inlineStr">
         <is>
           <t>€15k</t>
         </is>
       </c>
-      <c r="D51" s="35" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>€30k</t>
         </is>
       </c>
-      <c r="E51" s="35" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>€125k</t>
         </is>
       </c>
-      <c r="F51" s="35" t="inlineStr">
+      <c r="F53" s="35" t="inlineStr">
         <is>
           <t>€335k</t>
         </is>
       </c>
-      <c r="G51" s="35" t="inlineStr">
-        <is>
-          <t>€545k</t>
-        </is>
-      </c>
-      <c r="H51" s="35" t="inlineStr">
-        <is>
-          <t>€770k</t>
-        </is>
-      </c>
-      <c r="I51" s="35" t="inlineStr">
-        <is>
-          <t>€995k</t>
-        </is>
-      </c>
-      <c r="J51" s="35" t="inlineStr">
-        <is>
-          <t>€1.32M</t>
-        </is>
-      </c>
-      <c r="K51" s="35" t="inlineStr">
-        <is>
-          <t>€1.68M</t>
-        </is>
-      </c>
-      <c r="L51" s="36" t="inlineStr">
-        <is>
-          <t>€1.68M</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
+        <is>
+          <t>€560k</t>
+        </is>
+      </c>
+      <c r="H53" s="35" t="inlineStr">
+        <is>
+          <t>€785k</t>
+        </is>
+      </c>
+      <c r="I53" s="35" t="inlineStr">
+        <is>
+          <t>€1.01M</t>
+        </is>
+      </c>
+      <c r="J53" s="35" t="inlineStr">
+        <is>
+          <t>€1.33M</t>
+        </is>
+      </c>
+      <c r="K53" s="35" t="inlineStr">
+        <is>
+          <t>€1.71M</t>
+        </is>
+      </c>
+      <c r="L53" s="36" t="inlineStr">
+        <is>
+          <t>€1.71M</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>50 deals ÷ 10% = 500 meetings over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="18">
-        <f> 56/mo − 15 from SMB BDRs = 41 from dedicated BDRs</f>
-        <v/>
-      </c>
-    </row>
     <row r="56">
-      <c r="A56" s="37" t="inlineStr">
-        <is>
-          <t>41/mo ÷ 15/BDR = 3 dedicated MM BDRs needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>52 deals ÷ 10% = 520 meetings over 9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18">
+        <f> 58/mo − 15 from SMB BDRs = 43 from dedicated BDRs</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="37" t="inlineStr">
+        <is>
+          <t>43/mo ÷ 15/BDR = 3 dedicated MM BDRs needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 2: PUSH</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="19" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>Hit €2M — staggered hiring, one whale in the bag</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>NARRATIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="inlineStr">
-        <is>
-          <t>The push scenario targets €2M new deal ARR with three levers: an early AE hire in June, staggered reinforcements in August and October, and a large deal already in advanced pipeline closing in May. Victor goes full-time in June. Martijn stays at 0.5 FTE throughout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="21" t="inlineStr">
-        <is>
-          <t>The May large deal (€100K) is not speculative — it's an active opportunity already in late-stage pipeline. This anchors Q2 revenue and buys time for the June AE hire to ramp. By Q4, we have 4+ effective AEs producing across all three tiers. BDR scales to 5 with the SMB team contributing ~15 meetings/month on top.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
         <is>
-          <t>Risk profile: MEDIUM. The staggered hiring (Jun/Aug/Oct) gives us an exit ramp at each stage. If the June hire underperforms, we delay August. If close rates drop to 7%, we still land around €1.5M. Monthly burn peaks at €38K. But if the motion works and the May deal signals market readiness, we're past €2M with room to accelerate into 2027.</t>
+          <t>The push scenario targets €2M new deal ARR. Victor goes full-time in June. First new AE joins in June, a second in August, a third in October. Martijn increases to 0.5 FTE in August. A large deal already in advanced pipeline closes in May (€100K) — this anchors Q2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="inlineStr">
+        <is>
+          <t>Optional lever: depending on AE hiring quality and skillset, we may switch one SMB AE to MM in August. This adds 1.0 FTE at full productivity (no ramp needed) and could reduce the need for the October new hire. Decision point: end of July based on Q3 pipeline quality.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>Risk profile: MEDIUM. Monthly burn peaks at ~€38K. The staggered hiring gives exit ramps. If the June hire underperforms, we delay August. If close rates hold at 10%, we land at ~€2.1M. Expansion from pilot conversions adds upside. The SMB switch lever is insurance — if we use it, we can skip the October hire and still hit target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="20" t="inlineStr">
         <is>
           <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>Ramped: Martijn 0.2→0.5 (Aug), Mossel 0.2, Victor 0.2→1.0 (Jun)</t>
+        </is>
+      </c>
+      <c r="F70" s="46" t="inlineStr">
+        <is>
+          <t>SMB→MM switch: Aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B71" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D71" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="E71" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F71" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
+      <c r="G71" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H68" s="22" t="inlineStr">
+      <c r="H71" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I68" s="22" t="inlineStr">
+      <c r="I71" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J68" s="22" t="inlineStr">
+      <c r="J71" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K68" s="22" t="inlineStr">
+      <c r="K71" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L68" s="22" t="inlineStr">
+      <c r="L71" s="22" t="inlineStr">
         <is>
           <t>Peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C69" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D69" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K69" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L69" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="23" t="inlineStr">
-        <is>
-          <t>AEs (new hires)</t>
-        </is>
-      </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>cumulative</t>
-        </is>
-      </c>
-      <c r="C70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H70" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I70" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K70" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L70" s="26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="23" t="inlineStr">
-        <is>
-          <t>Effective AEs</t>
-        </is>
-      </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C71" s="27" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="D71" s="27" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="E71" s="27" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G71" s="27" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="H71" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="I71" s="27" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="K71" s="27" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="L71" s="26" t="inlineStr">
-        <is>
-          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
+          <t>AEs (ramped)</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>no ramp</t>
         </is>
       </c>
       <c r="C72" s="25" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D72" s="25" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E72" s="25" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="F72" s="25" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="G72" s="25" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="H72" s="25" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="I72" s="25" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J72" s="25" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="K72" s="25" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="L72" s="26" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C73" s="27" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D73" s="27" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="E73" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="G73" s="27" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="H73" s="27" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="I73" s="27" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="K73" s="27" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="L73" s="26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>AEs (new hires)</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>with ramp</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="23" t="inlineStr">
         <is>
+          <t>Effective AEs</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C74" s="27" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D74" s="27" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="G74" s="27" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="H74" s="27" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I74" s="27" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="J74" s="27" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="K74" s="27" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D75" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I75" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C76" s="27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" s="27" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E76" s="27" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="G76" s="27" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="H76" s="27" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="I76" s="27" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="J76" s="27" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="K76" s="27" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
           <t>Monthly cost</t>
         </is>
       </c>
-      <c r="C74" s="28" t="inlineStr">
-        <is>
-          <t>€5.8k</t>
-        </is>
-      </c>
-      <c r="D74" s="28" t="inlineStr">
-        <is>
-          <t>€8.2k</t>
-        </is>
-      </c>
-      <c r="E74" s="28" t="inlineStr">
-        <is>
-          <t>€23.0k</t>
-        </is>
-      </c>
-      <c r="F74" s="28" t="inlineStr">
-        <is>
-          <t>€27.0k</t>
-        </is>
-      </c>
-      <c r="G74" s="28" t="inlineStr">
-        <is>
-          <t>€37.0k</t>
-        </is>
-      </c>
-      <c r="H74" s="28" t="inlineStr">
-        <is>
-          <t>€37.0k</t>
-        </is>
-      </c>
-      <c r="I74" s="28" t="inlineStr">
-        <is>
-          <t>€41.0k</t>
-        </is>
-      </c>
-      <c r="J74" s="28" t="inlineStr">
-        <is>
-          <t>€47.0k</t>
-        </is>
-      </c>
-      <c r="K74" s="28" t="inlineStr">
-        <is>
-          <t>€47.0k</t>
-        </is>
-      </c>
-      <c r="L74" s="26" t="inlineStr">
-        <is>
-          <t>€273k total</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="20" t="inlineStr">
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>€5.2k</t>
+        </is>
+      </c>
+      <c r="D77" s="28" t="inlineStr">
+        <is>
+          <t>€7.6k</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>€22.4k</t>
+        </is>
+      </c>
+      <c r="F77" s="28" t="inlineStr">
+        <is>
+          <t>€26.4k</t>
+        </is>
+      </c>
+      <c r="G77" s="28" t="inlineStr">
+        <is>
+          <t>€38.2k</t>
+        </is>
+      </c>
+      <c r="H77" s="28" t="inlineStr">
+        <is>
+          <t>€38.2k</t>
+        </is>
+      </c>
+      <c r="I77" s="28" t="inlineStr">
+        <is>
+          <t>€42.2k</t>
+        </is>
+      </c>
+      <c r="J77" s="28" t="inlineStr">
+        <is>
+          <t>€48.2k</t>
+        </is>
+      </c>
+      <c r="K77" s="28" t="inlineStr">
+        <is>
+          <t>€48.2k</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="inlineStr">
+        <is>
+          <t>€277k total</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>DEAL FLOW</t>
         </is>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B79" s="24" t="inlineStr">
         <is>
           <t>from AE capacity</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="22" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B77" s="22" t="inlineStr"/>
-      <c r="C77" s="22" t="inlineStr">
+      <c r="B80" s="22" t="inlineStr"/>
+      <c r="C80" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D77" s="22" t="inlineStr">
+      <c r="D80" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E77" s="22" t="inlineStr">
+      <c r="E80" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F77" s="22" t="inlineStr">
+      <c r="F80" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G77" s="22" t="inlineStr">
+      <c r="G80" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H77" s="22" t="inlineStr">
+      <c r="H80" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I77" s="22" t="inlineStr">
+      <c r="I80" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J77" s="22" t="inlineStr">
+      <c r="J80" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K77" s="22" t="inlineStr">
+      <c r="K80" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L77" s="22" t="inlineStr">
+      <c r="L80" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="23" t="inlineStr">
-        <is>
-          <t>Pilots</t>
-        </is>
-      </c>
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C78" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F78" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="I78" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K78" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="L78" s="26" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>€50K ARR</t>
-        </is>
-      </c>
-      <c r="C79" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K79" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="26" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>€100K ARR</t>
-        </is>
-      </c>
-      <c r="C80" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="45" t="inlineStr">
-        <is>
-          <t>1*</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="26" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="23" t="inlineStr">
         <is>
+          <t>Pilots</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>€15K ARR</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G81" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H81" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I81" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K81" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>€50K ARR</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="45" t="inlineStr">
+        <is>
+          <t>1*</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="inlineStr">
+        <is>
           <t>Total deals closing</t>
         </is>
       </c>
-      <c r="C81" s="27" t="n">
+      <c r="C84" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="D81" s="27" t="n">
+      <c r="D84" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="27" t="n">
+      <c r="E84" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="F81" s="27" t="n">
+      <c r="F84" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="G81" s="27" t="n">
+      <c r="G84" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="H81" s="27" t="n">
+      <c r="H84" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I84" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J84" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K84" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>* = deal in pipeline (not from capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>PIPELINE NEEDED</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>2-mo cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr"/>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G88" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J88" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K88" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L88" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M88" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N88" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t>Deals closing</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>when they close</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H89" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I89" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="I81" s="27" t="n">
+      <c r="J89" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="J81" s="27" t="n">
+      <c r="K89" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L89" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="K81" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="L81" s="26" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="24" t="inlineStr">
-        <is>
-          <t>* = deal already in pipeline (not derived from capacity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B85" s="22" t="inlineStr"/>
-      <c r="C85" s="22" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E85" s="22" t="inlineStr">
+      <c r="M89" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="N89" s="29" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="23" t="inlineStr">
+        <is>
+          <t>SQLs needed</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>when to generate</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E90" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="F90" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G90" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="H90" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I90" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J90" s="43" t="n">
+        <v>110</v>
+      </c>
+      <c r="K90" s="43" t="n">
+        <v>120</v>
+      </c>
+      <c r="L90" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="44" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>ARR WATERFALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="inlineStr"/>
+      <c r="C93" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F85" s="22" t="inlineStr">
+      <c r="D93" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="G85" s="22" t="inlineStr">
+      <c r="E93" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="H85" s="22" t="inlineStr">
+      <c r="F93" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="I85" s="22" t="inlineStr">
+      <c r="G93" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="J85" s="22" t="inlineStr">
+      <c r="H93" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="K85" s="22" t="inlineStr">
+      <c r="I93" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="L85" s="22" t="inlineStr">
+      <c r="J93" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="M85" s="22" t="inlineStr">
+      <c r="K93" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="N85" s="22" t="inlineStr">
+      <c r="L93" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="23" t="inlineStr">
-        <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B86" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C86" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H86" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I86" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="J86" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="K86" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="L86" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="M86" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="N86" s="29" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="23" t="inlineStr">
-        <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C87" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D87" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E87" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F87" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G87" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="H87" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="I87" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="J87" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="K87" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="L87" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" s="44" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="inlineStr"/>
-      <c r="C90" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D90" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E90" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F90" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G90" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H90" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I90" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J90" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K90" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L90" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C91" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D91" s="30" t="inlineStr">
-        <is>
-          <t>€115k</t>
-        </is>
-      </c>
-      <c r="E91" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="F91" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="G91" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="H91" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="I91" s="30" t="inlineStr">
-        <is>
-          <t>€305k</t>
-        </is>
-      </c>
-      <c r="J91" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="K91" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="L91" s="29" t="inlineStr">
-        <is>
-          <t>€2.08M</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B92" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C92" s="38" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D92" s="38" t="inlineStr">
-        <is>
-          <t>€130k</t>
-        </is>
-      </c>
-      <c r="E92" s="38" t="inlineStr">
-        <is>
-          <t>€340k</t>
-        </is>
-      </c>
-      <c r="F92" s="38" t="inlineStr">
-        <is>
-          <t>€550k</t>
-        </is>
-      </c>
-      <c r="G92" s="38" t="inlineStr">
-        <is>
-          <t>€840k</t>
-        </is>
-      </c>
-      <c r="H92" s="38" t="inlineStr">
-        <is>
-          <t>€1.13M</t>
-        </is>
-      </c>
-      <c r="I92" s="38" t="inlineStr">
-        <is>
-          <t>€1.44M</t>
-        </is>
-      </c>
-      <c r="J92" s="38" t="inlineStr">
-        <is>
-          <t>€1.75M</t>
-        </is>
-      </c>
-      <c r="K92" s="38" t="inlineStr">
-        <is>
-          <t>€2.08M</t>
-        </is>
-      </c>
-      <c r="L92" s="41" t="inlineStr">
-        <is>
-          <t>€2.08M</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="23" t="inlineStr">
-        <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B93" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="K93" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="L93" s="42" t="inlineStr">
-        <is>
-          <t>+€140k</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="23" t="inlineStr">
         <is>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C94" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D94" s="30" t="inlineStr">
+        <is>
+          <t>€115k</t>
+        </is>
+      </c>
+      <c r="E94" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="F94" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="G94" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="H94" s="30" t="inlineStr">
+        <is>
+          <t>€305k</t>
+        </is>
+      </c>
+      <c r="I94" s="30" t="inlineStr">
+        <is>
+          <t>€305k</t>
+        </is>
+      </c>
+      <c r="J94" s="30" t="inlineStr">
+        <is>
+          <t>€320k</t>
+        </is>
+      </c>
+      <c r="K94" s="30" t="inlineStr">
+        <is>
+          <t>€335k</t>
+        </is>
+      </c>
+      <c r="L94" s="29" t="inlineStr">
+        <is>
+          <t>€2.10M</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="inlineStr">
+        <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B95" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C95" s="38" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D95" s="38" t="inlineStr">
+        <is>
+          <t>€130k</t>
+        </is>
+      </c>
+      <c r="E95" s="38" t="inlineStr">
+        <is>
+          <t>€340k</t>
+        </is>
+      </c>
+      <c r="F95" s="38" t="inlineStr">
+        <is>
+          <t>€550k</t>
+        </is>
+      </c>
+      <c r="G95" s="38" t="inlineStr">
+        <is>
+          <t>€840k</t>
+        </is>
+      </c>
+      <c r="H95" s="38" t="inlineStr">
+        <is>
+          <t>€1.15M</t>
+        </is>
+      </c>
+      <c r="I95" s="38" t="inlineStr">
+        <is>
+          <t>€1.45M</t>
+        </is>
+      </c>
+      <c r="J95" s="38" t="inlineStr">
+        <is>
+          <t>€1.77M</t>
+        </is>
+      </c>
+      <c r="K95" s="38" t="inlineStr">
+        <is>
+          <t>€2.10M</t>
+        </is>
+      </c>
+      <c r="L95" s="41" t="inlineStr">
+        <is>
+          <t>€2.10M</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B96" s="24" t="inlineStr">
+        <is>
+          <t>upside</t>
+        </is>
+      </c>
+      <c r="C96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J96" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="K96" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="L96" s="42" t="inlineStr">
+        <is>
+          <t>+€140k</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C94" s="35" t="inlineStr">
+      <c r="C97" s="35" t="inlineStr">
         <is>
           <t>€15k</t>
         </is>
       </c>
-      <c r="D94" s="35" t="inlineStr">
+      <c r="D97" s="35" t="inlineStr">
         <is>
           <t>€130k</t>
         </is>
       </c>
-      <c r="E94" s="35" t="inlineStr">
+      <c r="E97" s="35" t="inlineStr">
         <is>
           <t>€340k</t>
         </is>
       </c>
-      <c r="F94" s="35" t="inlineStr">
+      <c r="F97" s="35" t="inlineStr">
         <is>
           <t>€550k</t>
         </is>
       </c>
-      <c r="G94" s="35" t="inlineStr">
+      <c r="G97" s="35" t="inlineStr">
         <is>
           <t>€840k</t>
         </is>
       </c>
-      <c r="H94" s="35" t="inlineStr">
-        <is>
-          <t>€1.13M</t>
-        </is>
-      </c>
-      <c r="I94" s="35" t="inlineStr">
-        <is>
-          <t>€1.44M</t>
-        </is>
-      </c>
-      <c r="J94" s="35" t="inlineStr">
-        <is>
-          <t>€1.82M</t>
-        </is>
-      </c>
-      <c r="K94" s="35" t="inlineStr">
-        <is>
-          <t>€2.21M</t>
-        </is>
-      </c>
-      <c r="L94" s="36" t="inlineStr">
-        <is>
-          <t>€2.21M</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="20" t="inlineStr">
+      <c r="H97" s="35" t="inlineStr">
+        <is>
+          <t>€1.15M</t>
+        </is>
+      </c>
+      <c r="I97" s="35" t="inlineStr">
+        <is>
+          <t>€1.45M</t>
+        </is>
+      </c>
+      <c r="J97" s="35" t="inlineStr">
+        <is>
+          <t>€1.84M</t>
+        </is>
+      </c>
+      <c r="K97" s="35" t="inlineStr">
+        <is>
+          <t>€2.25M</t>
+        </is>
+      </c>
+      <c r="L97" s="36" t="inlineStr">
+        <is>
+          <t>€2.25M</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="18" t="inlineStr">
-        <is>
-          <t>65 deals ÷ 10% = 650 meetings over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="18">
-        <f> 73/mo − 15 from SMB BDRs = 58 from dedicated BDRs</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="37" t="inlineStr">
-        <is>
-          <t>58/mo ÷ 15/BDR = 4 dedicated MM BDRs needed</t>
-        </is>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>67 deals ÷ 10% = 670 meetings over 9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18">
+        <f> 75/mo − 15 from SMB BDRs = 60 from dedicated BDRs</f>
+        <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="17" t="inlineStr">
+      <c r="A102" s="37" t="inlineStr">
+        <is>
+          <t>60/mo ÷ 15/BDR = 4 dedicated MM BDRs needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="47" t="inlineStr">
+        <is>
+          <t>IF SMB→MM SWITCH ACTIVATED (Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>Drops Oct new hire. New deal ARR: €2.51M | Total: €2.65M | Saves 1 new hire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="24" t="inlineStr">
+        <is>
+          <t>Effective AEs: ['0.6', '0.6', '1.9', '2.1', '4.2', '4.5', '4.7', '4.7', '4.7']</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 3: HYPER-PUSH</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="19" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>Build the €3M machine — staff it like a proven motion</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>NARRATIVE</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="21" t="inlineStr">
-        <is>
-          <t>Maximum conviction. Victor goes full-time in May (one month early). The May large deal anchors Q2 at €100K+. First new AE in June, two more in July, two more in September, another in November. Martijn stays at 0.5 FTE throughout. BDR team scales to 6 by Q4. Combined with SMB spillover, we're generating 115+ MM meetings/month by October.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="inlineStr">
-        <is>
-          <t>This requires an MM team lead by August — someone who can run pipeline reviews, maintain process quality across 7+ AEs, and own the weekly forecast. Without that hire, AE variance will kill the model. We also need solutioning capacity for 3+ large deals in parallel by Q4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="inlineStr">
-        <is>
-          <t>Risk profile: HIGH. Monthly burn hits €62K by December. Total 9-month cost: ~€385K. But the output targets €3.3M new deal ARR + expansion. That's a 9x return on the hiring investment and puts MM on track for a €5M+ run-rate entering 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="21" t="inlineStr">
+        <is>
+          <t>Maximum conviction. Victor goes full-time in May. The May large deal anchors Q2. First new AE in June, two more in July, two more in September, another in November. Martijn goes to 0.5 FTE in August. An SMB AE switches to MM in August — no ramp needed. BDR scales to 6 by Q4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="inlineStr">
+        <is>
+          <t>This requires an MM team lead by August — someone who can run pipeline reviews, maintain process quality across 7+ AEs, and own the weekly forecast. We also need solutioning capacity for 3+ large deals in parallel by Q4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="inlineStr">
+        <is>
+          <t>Risk profile: HIGH. Monthly burn hits ~€65K by December. But the output targets €3.3M+ new deal ARR. The SMB switch adds immediate capacity without ramp cost — it's the highest-leverage move if we have the right person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="20" t="inlineStr">
         <is>
           <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="22" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="24" t="inlineStr">
+        <is>
+          <t>Ramped: Martijn 0.2→0.5 (Aug), Mossel 0.2, Victor 0.2→1.0 (May), +1 SMB→MM (Aug)</t>
+        </is>
+      </c>
+      <c r="F118" s="46" t="inlineStr">
+        <is>
+          <t>SMB→MM switch: Aug (committed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="22" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B111" s="22" t="inlineStr">
+      <c r="B119" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C111" s="22" t="inlineStr">
+      <c r="C119" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D111" s="22" t="inlineStr">
+      <c r="D119" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E111" s="22" t="inlineStr">
+      <c r="E119" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F111" s="22" t="inlineStr">
+      <c r="F119" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G111" s="22" t="inlineStr">
+      <c r="G119" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H111" s="22" t="inlineStr">
+      <c r="H119" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I111" s="22" t="inlineStr">
+      <c r="I119" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J111" s="22" t="inlineStr">
+      <c r="J119" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K111" s="22" t="inlineStr">
+      <c r="K119" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L111" s="22" t="inlineStr">
+      <c r="L119" s="22" t="inlineStr">
         <is>
           <t>Peak</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="23" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="23" t="inlineStr">
         <is>
           <t>AEs (ramped)</t>
         </is>
       </c>
-      <c r="B112" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C112" s="25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K112" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L112" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="23" t="inlineStr">
-        <is>
-          <t>AEs (new hires)</t>
-        </is>
-      </c>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>cumulative</t>
-        </is>
-      </c>
-      <c r="C113" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G113" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H113" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I113" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K113" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L113" s="26" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="23" t="inlineStr">
-        <is>
-          <t>Effective AEs</t>
-        </is>
-      </c>
-      <c r="B114" s="24" t="inlineStr">
-        <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C114" s="27" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="D114" s="27" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="E114" s="27" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="F114" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="G114" s="27" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="H114" s="27" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="I114" s="27" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="J114" s="27" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="K114" s="27" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="L114" s="26" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="23" t="inlineStr">
-        <is>
-          <t>BDRs (dedicated)</t>
-        </is>
-      </c>
-      <c r="B115" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C115" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D115" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F115" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G115" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H115" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I115" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J115" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K115" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L115" s="26" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="23" t="inlineStr">
-        <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C116" s="27" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D116" s="27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E116" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="F116" s="27" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="G116" s="27" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="H116" s="27" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="I116" s="27" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
-      </c>
-      <c r="J116" s="27" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="K116" s="27" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="L116" s="26" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="23" t="inlineStr">
-        <is>
-          <t>Monthly cost</t>
-        </is>
-      </c>
-      <c r="C117" s="28" t="inlineStr">
-        <is>
-          <t>€5.8k</t>
-        </is>
-      </c>
-      <c r="D117" s="28" t="inlineStr">
-        <is>
-          <t>€13.0k</t>
-        </is>
-      </c>
-      <c r="E117" s="28" t="inlineStr">
-        <is>
-          <t>€23.0k</t>
-        </is>
-      </c>
-      <c r="F117" s="28" t="inlineStr">
-        <is>
-          <t>€39.0k</t>
-        </is>
-      </c>
-      <c r="G117" s="28" t="inlineStr">
-        <is>
-          <t>€43.0k</t>
-        </is>
-      </c>
-      <c r="H117" s="28" t="inlineStr">
-        <is>
-          <t>€59.0k</t>
-        </is>
-      </c>
-      <c r="I117" s="28" t="inlineStr">
-        <is>
-          <t>€63.0k</t>
-        </is>
-      </c>
-      <c r="J117" s="28" t="inlineStr">
-        <is>
-          <t>€69.0k</t>
-        </is>
-      </c>
-      <c r="K117" s="28" t="inlineStr">
-        <is>
-          <t>€69.0k</t>
-        </is>
-      </c>
-      <c r="L117" s="26" t="inlineStr">
-        <is>
-          <t>€384k total</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
-        <is>
-          <t>DEAL FLOW</t>
-        </is>
-      </c>
-      <c r="B119" s="24" t="inlineStr">
-        <is>
-          <t>from AE capacity</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="22" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="inlineStr"/>
-      <c r="C120" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D120" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E120" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G120" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H120" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I120" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J120" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K120" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L120" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>no ramp</t>
+        </is>
+      </c>
+      <c r="C120" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D120" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E120" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F120" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G120" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H120" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I120" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J120" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K120" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L120" s="26" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>Pilots</t>
+          <t>AEs (new hires)</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C121" s="28" t="n">
+          <t>with ramp</t>
+        </is>
+      </c>
+      <c r="C121" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D121" s="28" t="n">
+      <c r="F121" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E121" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F121" s="28" t="n">
+      <c r="G121" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I121" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J121" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="G121" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="H121" s="28" t="n">
-        <v>11</v>
-      </c>
-      <c r="I121" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="J121" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="K121" s="28" t="n">
-        <v>14</v>
+      <c r="K121" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="L121" s="26" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Effective AEs</t>
         </is>
       </c>
       <c r="B122" s="24" t="inlineStr">
         <is>
-          <t>€50K ARR</t>
-        </is>
-      </c>
-      <c r="C122" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G122" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H122" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I122" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="K122" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L122" s="26" t="n">
-        <v>20</v>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C122" s="27" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D122" s="27" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="E122" s="27" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="F122" s="27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="G122" s="27" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="H122" s="27" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="I122" s="27" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="J122" s="27" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="K122" s="27" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L122" s="26" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>BDRs (dedicated)</t>
         </is>
       </c>
       <c r="B123" s="24" t="inlineStr">
         <is>
-          <t>€100K ARR</t>
-        </is>
-      </c>
-      <c r="C123" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="45" t="inlineStr">
-        <is>
-          <t>1*</t>
-        </is>
-      </c>
-      <c r="E123" s="28" t="n">
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C123" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D123" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="28" t="n">
+      <c r="E123" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="I123" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J123" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K123" s="28" t="n">
-        <v>2</v>
+      <c r="F123" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I123" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J123" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K123" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="L123" s="26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="23" t="inlineStr">
         <is>
-          <t>Total deals closing</t>
-        </is>
-      </c>
-      <c r="C124" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E124" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="F124" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="G124" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="H124" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="I124" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="J124" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="K124" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="L124" s="26" t="n">
-        <v>105</v>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C124" s="27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D124" s="27" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="E124" s="27" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="F124" s="27" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="G124" s="27" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="H124" s="27" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="I124" s="27" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="J124" s="27" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="K124" s="27" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="L124" s="26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="24" t="inlineStr">
-        <is>
-          <t>* = deal already in pipeline (not derived from capacity)</t>
+      <c r="A125" s="23" t="inlineStr">
+        <is>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>€5.2k</t>
+        </is>
+      </c>
+      <c r="D125" s="28" t="inlineStr">
+        <is>
+          <t>€12.4k</t>
+        </is>
+      </c>
+      <c r="E125" s="28" t="inlineStr">
+        <is>
+          <t>€22.4k</t>
+        </is>
+      </c>
+      <c r="F125" s="28" t="inlineStr">
+        <is>
+          <t>€38.4k</t>
+        </is>
+      </c>
+      <c r="G125" s="28" t="inlineStr">
+        <is>
+          <t>€50.2k</t>
+        </is>
+      </c>
+      <c r="H125" s="28" t="inlineStr">
+        <is>
+          <t>€66.2k</t>
+        </is>
+      </c>
+      <c r="I125" s="28" t="inlineStr">
+        <is>
+          <t>€70.2k</t>
+        </is>
+      </c>
+      <c r="J125" s="28" t="inlineStr">
+        <is>
+          <t>€76.2k</t>
+        </is>
+      </c>
+      <c r="K125" s="28" t="inlineStr">
+        <is>
+          <t>€76.2k</t>
+        </is>
+      </c>
+      <c r="L125" s="26" t="inlineStr">
+        <is>
+          <t>€417k total</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>PIPELINE NEEDED</t>
+          <t>DEAL FLOW</t>
         </is>
       </c>
       <c r="B127" s="24" t="inlineStr">
         <is>
-          <t>2-mo cycle</t>
+          <t>from AE capacity</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B128" s="22" t="inlineStr"/>
       <c r="C128" s="22" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="E128" s="22" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F128" s="22" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="G128" s="22" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="H128" s="22" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="I128" s="22" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="J128" s="22" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="K128" s="22" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="L128" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M128" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N128" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -6184,458 +6005,711 @@
     <row r="129">
       <c r="A129" s="23" t="inlineStr">
         <is>
-          <t>Deals closing</t>
+          <t>Pilots</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C129" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="30" t="n">
+          <t>€15K ARR</t>
+        </is>
+      </c>
+      <c r="C129" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F129" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G129" s="30" t="n">
+      <c r="D129" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="H129" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="I129" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="J129" s="30" t="n">
+      <c r="G129" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H129" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="I129" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="J129" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="K129" s="30" t="n">
+      <c r="K129" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="L129" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="M129" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="N129" s="29" t="n">
-        <v>105</v>
+      <c r="L129" s="26" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="23" t="inlineStr">
         <is>
-          <t>SQLs needed</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B130" s="24" t="inlineStr">
         <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C130" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D130" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E130" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F130" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="G130" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="H130" s="43" t="n">
-        <v>160</v>
-      </c>
-      <c r="I130" s="43" t="n">
-        <v>170</v>
-      </c>
-      <c r="J130" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="K130" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="L130" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N130" s="44" t="n">
-        <v>1050</v>
+          <t>€50K ARR</t>
+        </is>
+      </c>
+      <c r="C130" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H130" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J130" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K130" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="23" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B131" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="45" t="inlineStr">
+        <is>
+          <t>1*</t>
+        </is>
+      </c>
+      <c r="E131" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K131" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" s="26" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
+      <c r="A132" s="23" t="inlineStr">
+        <is>
+          <t>Total deals closing</t>
+        </is>
+      </c>
+      <c r="C132" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E132" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F132" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G132" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H132" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="I132" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J132" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="K132" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B133" s="22" t="inlineStr"/>
-      <c r="C133" s="22" t="inlineStr">
+      <c r="A133" s="24" t="inlineStr">
+        <is>
+          <t>* = deal in pipeline (not from capacity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>PIPELINE NEEDED</t>
+        </is>
+      </c>
+      <c r="B135" s="24" t="inlineStr">
+        <is>
+          <t>2-mo cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B136" s="22" t="inlineStr"/>
+      <c r="C136" s="22" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E136" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D133" s="22" t="inlineStr">
+      <c r="F136" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E133" s="22" t="inlineStr">
+      <c r="G136" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F133" s="22" t="inlineStr">
+      <c r="H136" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G133" s="22" t="inlineStr">
+      <c r="I136" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H133" s="22" t="inlineStr">
+      <c r="J136" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I133" s="22" t="inlineStr">
+      <c r="K136" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J133" s="22" t="inlineStr">
+      <c r="L136" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K133" s="22" t="inlineStr">
+      <c r="M136" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L133" s="22" t="inlineStr">
+      <c r="N136" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C134" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D134" s="30" t="inlineStr">
-        <is>
-          <t>€195k</t>
-        </is>
-      </c>
-      <c r="E134" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="F134" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="G134" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="H134" s="30" t="inlineStr">
-        <is>
-          <t>€515k</t>
-        </is>
-      </c>
-      <c r="I134" s="30" t="inlineStr">
-        <is>
-          <t>€530k</t>
-        </is>
-      </c>
-      <c r="J134" s="30" t="inlineStr">
-        <is>
-          <t>€610k</t>
-        </is>
-      </c>
-      <c r="K134" s="30" t="inlineStr">
-        <is>
-          <t>€610k</t>
-        </is>
-      </c>
-      <c r="L134" s="29" t="inlineStr">
-        <is>
-          <t>€3.29M</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B135" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C135" s="38" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D135" s="38" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="E135" s="38" t="inlineStr">
-        <is>
-          <t>€420k</t>
-        </is>
-      </c>
-      <c r="F135" s="38" t="inlineStr">
-        <is>
-          <t>€710k</t>
-        </is>
-      </c>
-      <c r="G135" s="38" t="inlineStr">
-        <is>
-          <t>€1.03M</t>
-        </is>
-      </c>
-      <c r="H135" s="38" t="inlineStr">
-        <is>
-          <t>€1.54M</t>
-        </is>
-      </c>
-      <c r="I135" s="38" t="inlineStr">
-        <is>
-          <t>€2.08M</t>
-        </is>
-      </c>
-      <c r="J135" s="38" t="inlineStr">
-        <is>
-          <t>€2.69M</t>
-        </is>
-      </c>
-      <c r="K135" s="38" t="inlineStr">
-        <is>
-          <t>€3.29M</t>
-        </is>
-      </c>
-      <c r="L135" s="41" t="inlineStr">
-        <is>
-          <t>€3.29M</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="23" t="inlineStr">
-        <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B136" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C136" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D136" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E136" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I136" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="J136" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="K136" s="34" t="inlineStr">
-        <is>
-          <t>€155k</t>
-        </is>
-      </c>
-      <c r="L136" s="42" t="inlineStr">
-        <is>
-          <t>+€260k</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="23" t="inlineStr">
         <is>
+          <t>Deals closing</t>
+        </is>
+      </c>
+      <c r="B137" s="24" t="inlineStr">
+        <is>
+          <t>when they close</t>
+        </is>
+      </c>
+      <c r="C137" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D137" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E137" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G137" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H137" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="I137" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="J137" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="K137" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="L137" s="30" t="n">
+        <v>23</v>
+      </c>
+      <c r="M137" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="N137" s="29" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="23" t="inlineStr">
+        <is>
+          <t>SQLs needed</t>
+        </is>
+      </c>
+      <c r="B138" s="24" t="inlineStr">
+        <is>
+          <t>when to generate</t>
+        </is>
+      </c>
+      <c r="C138" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="D138" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E138" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="F138" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="G138" s="43" t="n">
+        <v>150</v>
+      </c>
+      <c r="H138" s="43" t="n">
+        <v>180</v>
+      </c>
+      <c r="I138" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="J138" s="43" t="n">
+        <v>230</v>
+      </c>
+      <c r="K138" s="43" t="n">
+        <v>240</v>
+      </c>
+      <c r="L138" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M138" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="44" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>ARR WATERFALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B141" s="22" t="inlineStr"/>
+      <c r="C141" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F141" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G141" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H141" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I141" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J141" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K141" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L141" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="23" t="inlineStr">
+        <is>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C142" s="30" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D142" s="30" t="inlineStr">
+        <is>
+          <t>€195k</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>€290k</t>
+        </is>
+      </c>
+      <c r="G142" s="30" t="inlineStr">
+        <is>
+          <t>€500k</t>
+        </is>
+      </c>
+      <c r="H142" s="30" t="inlineStr">
+        <is>
+          <t>€545k</t>
+        </is>
+      </c>
+      <c r="I142" s="30" t="inlineStr">
+        <is>
+          <t>€610k</t>
+        </is>
+      </c>
+      <c r="J142" s="30" t="inlineStr">
+        <is>
+          <t>€740k</t>
+        </is>
+      </c>
+      <c r="K142" s="30" t="inlineStr">
+        <is>
+          <t>€755k</t>
+        </is>
+      </c>
+      <c r="L142" s="29" t="inlineStr">
+        <is>
+          <t>€3.86M</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="23" t="inlineStr">
+        <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B143" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C143" s="38" t="inlineStr">
+        <is>
+          <t>€15k</t>
+        </is>
+      </c>
+      <c r="D143" s="38" t="inlineStr">
+        <is>
+          <t>€210k</t>
+        </is>
+      </c>
+      <c r="E143" s="38" t="inlineStr">
+        <is>
+          <t>€420k</t>
+        </is>
+      </c>
+      <c r="F143" s="38" t="inlineStr">
+        <is>
+          <t>€710k</t>
+        </is>
+      </c>
+      <c r="G143" s="38" t="inlineStr">
+        <is>
+          <t>€1.21M</t>
+        </is>
+      </c>
+      <c r="H143" s="38" t="inlineStr">
+        <is>
+          <t>€1.75M</t>
+        </is>
+      </c>
+      <c r="I143" s="38" t="inlineStr">
+        <is>
+          <t>€2.37M</t>
+        </is>
+      </c>
+      <c r="J143" s="38" t="inlineStr">
+        <is>
+          <t>€3.10M</t>
+        </is>
+      </c>
+      <c r="K143" s="38" t="inlineStr">
+        <is>
+          <t>€3.86M</t>
+        </is>
+      </c>
+      <c r="L143" s="41" t="inlineStr">
+        <is>
+          <t>€3.86M</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B144" s="24" t="inlineStr">
+        <is>
+          <t>upside</t>
+        </is>
+      </c>
+      <c r="C144" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D144" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E144" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="34" t="inlineStr">
+        <is>
+          <t>€35k</t>
+        </is>
+      </c>
+      <c r="J144" s="34" t="inlineStr">
+        <is>
+          <t>€70k</t>
+        </is>
+      </c>
+      <c r="K144" s="34" t="inlineStr">
+        <is>
+          <t>€155k</t>
+        </is>
+      </c>
+      <c r="L144" s="42" t="inlineStr">
+        <is>
+          <t>+€260k</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C137" s="35" t="inlineStr">
+      <c r="C145" s="35" t="inlineStr">
         <is>
           <t>€15k</t>
         </is>
       </c>
-      <c r="D137" s="35" t="inlineStr">
+      <c r="D145" s="35" t="inlineStr">
         <is>
           <t>€210k</t>
         </is>
       </c>
-      <c r="E137" s="35" t="inlineStr">
+      <c r="E145" s="35" t="inlineStr">
         <is>
           <t>€420k</t>
         </is>
       </c>
-      <c r="F137" s="35" t="inlineStr">
+      <c r="F145" s="35" t="inlineStr">
         <is>
           <t>€710k</t>
         </is>
       </c>
-      <c r="G137" s="35" t="inlineStr">
-        <is>
-          <t>€1.03M</t>
-        </is>
-      </c>
-      <c r="H137" s="35" t="inlineStr">
-        <is>
-          <t>€1.54M</t>
-        </is>
-      </c>
-      <c r="I137" s="35" t="inlineStr">
-        <is>
-          <t>€2.11M</t>
-        </is>
-      </c>
-      <c r="J137" s="35" t="inlineStr">
-        <is>
-          <t>€2.79M</t>
-        </is>
-      </c>
-      <c r="K137" s="35" t="inlineStr">
-        <is>
-          <t>€3.56M</t>
-        </is>
-      </c>
-      <c r="L137" s="36" t="inlineStr">
-        <is>
-          <t>€3.56M</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="20" t="inlineStr">
+      <c r="G145" s="35" t="inlineStr">
+        <is>
+          <t>€1.21M</t>
+        </is>
+      </c>
+      <c r="H145" s="35" t="inlineStr">
+        <is>
+          <t>€1.75M</t>
+        </is>
+      </c>
+      <c r="I145" s="35" t="inlineStr">
+        <is>
+          <t>€2.40M</t>
+        </is>
+      </c>
+      <c r="J145" s="35" t="inlineStr">
+        <is>
+          <t>€3.21M</t>
+        </is>
+      </c>
+      <c r="K145" s="35" t="inlineStr">
+        <is>
+          <t>€4.12M</t>
+        </is>
+      </c>
+      <c r="L145" s="36" t="inlineStr">
+        <is>
+          <t>€4.12M</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
         <is>
           <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="18" t="inlineStr">
-        <is>
-          <t>105 deals ÷ 10% = 1050 meetings over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="18">
-        <f> 117/mo − 15 from SMB BDRs = 102 from dedicated BDRs</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="37" t="inlineStr">
-        <is>
-          <t>102/mo ÷ 15/BDR = 7 dedicated MM BDRs needed</t>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>121 deals ÷ 10% = 1210 meetings over 9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="18">
+        <f> 135/mo − 15 from SMB BDRs = 120 from dedicated BDRs</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="37" t="inlineStr">
+        <is>
+          <t>120/mo ÷ 15/BDR = 8 dedicated MM BDRs needed</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A64:K64"/>
+  <mergeCells count="21">
+    <mergeCell ref="A114:K114"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A24:K24"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A107:K107"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A108:K108"/>
+    <mergeCell ref="A66:K66"/>
     <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A113:K113"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A106:K106"/>
     <mergeCell ref="A8:K8"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A115:K115"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/work/WP_SEO_AI_Scenario_Planning.xlsx
+++ b/work/WP_SEO_AI_Scenario_Planning.xlsx
@@ -152,7 +152,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -214,6 +214,12 @@
         <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -238,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -331,6 +337,27 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3025,609 +3052,712 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N150"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>MM — Scenario Planning</t>
+          <t>MM — Scenario Planning (formula-driven)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>ASSUMPTIONS</t>
+          <t>PARAMETERS (edit yellow → all scenarios update)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>Yellow cells = inputs. Green cells = computed.</t>
-        </is>
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>ARR Pilot (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Per fully ramped AE: €240K/quarter = €80K/month.</t>
-        </is>
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>ARR Medium (€)</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Deal cadence per AE/month: 2 pilots (€15K) + 1 medium per 2 months (€50K) + 1 large per quarter (€100K).</t>
-        </is>
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>ARR Large (€)</t>
+        </is>
+      </c>
+      <c r="C6" s="48" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>New AE ramp: 50% → 75% → 100% over 3 months. Existing AEs (incl. SMB→MM switch) = no ramp.</t>
-        </is>
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Close rate (blended)</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Martijn: 0.2 FTE Apr-Jul, 0.5 FTE Aug+. Mossel: 0.2 FTE throughout. Victor: 0.2→1.0 FTE.</t>
-        </is>
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>BDR meetings/mo cap</t>
+        </is>
+      </c>
+      <c r="C8" s="48" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>Optional lever: switch 1 SMB AE to MM (no ramp needed). Decision point: end of July.</t>
-        </is>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>SMB BDR free mtgs/mo</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Blended close rate: 10% (meeting → deal). Deal type determined during sales process.</t>
-        </is>
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>AE cost/mo (€)</t>
+        </is>
+      </c>
+      <c r="C10" s="48" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>SMB BDR team contributes ~15 MM meetings/month (free pipeline).</t>
-        </is>
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>BDR cost/mo (€)</t>
+        </is>
+      </c>
+      <c r="C11" s="48" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Deal cycle: 2 months (SQL → close). Pipeline row shows when SQLs must be generated.</t>
-        </is>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Ramp month 1</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Pilot conversion at month 5: 40% → Medium, 10% → Large. Expansion = upside, not counted toward €2M.</t>
-        </is>
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Ramp month 2</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>AE cost: €6K/mo. BDR cost: €4K/mo.</t>
-        </is>
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Ramp month 3+</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Push scenario includes 1 large deal closing in May (currently in advanced pipeline).</t>
-        </is>
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Pilot conv → Med</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Pilot conv → Large</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Deals/AE/mo: pilots</t>
+        </is>
+      </c>
+      <c r="C17" s="48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Deals/AE/mo: medium</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Deals/AE/mo: large</t>
+        </is>
+      </c>
+      <c r="C19" s="48" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 1: BASELINE</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>Conservative ramp — prove the motion, then scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NARRATIVE</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>We start with 0.6 FTE AE capacity (Martijn 0.2 + Mossel 0.2 + Victor 0.2) and 0.4 FTE BDR. Victor goes full-time in June, giving us 1.4 effective AEs. Martijn increases to 0.5 FTE in August. One new AE joins in July, a second in October. BDR scales to 3 by Q4, supplemented by ~15 MM meetings/month from the SMB BDR team.</t>
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Conservative — prove it, then scale</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>This is the 'prove it before you scale' path. We close our first pilots in May-June, get the narrative tested in 20+ meetings, and let the month-5 pilot reviews (starting September) validate the conversion thesis before committing to more headcount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Risk profile: LOW. Total cost under €185K. Downside: ~€1.6M new deal ARR — short of €2M but with a proven playbook and clear signal on what to accelerate in Q1 2027.</t>
+          <t>Martijn 0.2→0.5(Aug), Mossel 0.2, Victor 0.2→1.0(Jun). 2 new hires (Jul, Oct). BDR to 3. Risk: LOW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>HEADCOUNT</t>
+      <c r="A26" s="22" t="inlineStr"/>
+      <c r="B26" s="22" t="inlineStr"/>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>Peak</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>Ramped: Martijn 0.2→0.5 (Aug), Mossel 0.2, Victor 0.2→1.0 (Jun)</t>
-        </is>
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>AEs (ramped)</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>no ramp</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D27" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F27" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H27" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I27" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J27" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K27" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L27" s="28">
+        <f>MAX(C27:K27)</f>
+        <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L28" s="22" t="inlineStr">
-        <is>
-          <t>Peak</t>
-        </is>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>AEs (new hires)</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="28">
+        <f>MAX(C28:K28)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>no ramp</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F29" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H29" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I29" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J29" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K29" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L29" s="26" t="n">
-        <v>1.7</v>
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  added this month</t>
+        </is>
+      </c>
+      <c r="C29" s="50">
+        <f>MAX(0,C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="50">
+        <f>MAX(0,D28-C28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="50">
+        <f>MAX(0,E28-D28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="50">
+        <f>MAX(0,F28-E28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="50">
+        <f>MAX(0,G28-F28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="50">
+        <f>MAX(0,H28-G28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="50">
+        <f>MAX(0,I28-H28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="50">
+        <f>MAX(0,J28-I28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="50">
+        <f>MAX(0,K28-J28)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>AEs (new hires)</t>
+          <t>Effective AEs</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>with ramp</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="26" t="n">
-        <v>2</v>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C30" s="28">
+        <f>C27+C29*$C$12</f>
+        <v/>
+      </c>
+      <c r="D30" s="28">
+        <f>D27+D29*$C$12+C29*$C$13</f>
+        <v/>
+      </c>
+      <c r="E30" s="28">
+        <f>E27+E29*$C$12+D29*$C$13+SUM(C29:C29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="F30" s="28">
+        <f>F27+F29*$C$12+E29*$C$13+SUM(C29:D29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="G30" s="28">
+        <f>G27+G29*$C$12+F29*$C$13+SUM(C29:E29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="H30" s="28">
+        <f>H27+H29*$C$12+G29*$C$13+SUM(C29:F29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="I30" s="28">
+        <f>I27+I29*$C$12+H29*$C$13+SUM(C29:G29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="J30" s="28">
+        <f>J27+J29*$C$12+I29*$C$13+SUM(C29:H29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="K30" s="28">
+        <f>K27+K29*$C$12+J29*$C$13+SUM(C29:I29)*$C$14</f>
+        <v/>
+      </c>
+      <c r="L30" s="28">
+        <f>MAX(C30:K30)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Effective AEs</t>
+          <t>BDRs (dedicated)</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D31" s="27" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="E31" s="27" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="G31" s="27" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="K31" s="27" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="L31" s="26" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" s="28">
+        <f>MAX(C31:K31)</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D32" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E32" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K32" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L32" s="26" t="n">
-        <v>3</v>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C32" s="28">
+        <f>C27+C28+C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="28">
+        <f>D27+D28+D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>E27+E28+E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>F27+F28+F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="28">
+        <f>G27+G28+G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="28">
+        <f>H27+H28+H31</f>
+        <v/>
+      </c>
+      <c r="I32" s="28">
+        <f>I27+I28+I31</f>
+        <v/>
+      </c>
+      <c r="J32" s="28">
+        <f>J27+J28+J31</f>
+        <v/>
+      </c>
+      <c r="K32" s="28">
+        <f>K27+K28+K31</f>
+        <v/>
+      </c>
+      <c r="L32" s="28">
+        <f>MAX(C32:K32)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="G33" s="27" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="I33" s="27" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="K33" s="27" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
           <t>Monthly cost</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
-        <is>
-          <t>€5.2k</t>
-        </is>
-      </c>
-      <c r="D34" s="28" t="inlineStr">
-        <is>
-          <t>€5.2k</t>
-        </is>
-      </c>
-      <c r="E34" s="28" t="inlineStr">
-        <is>
-          <t>€12.4k</t>
-        </is>
-      </c>
-      <c r="F34" s="28" t="inlineStr">
-        <is>
-          <t>€18.4k</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="inlineStr">
-        <is>
-          <t>€24.2k</t>
-        </is>
-      </c>
-      <c r="H34" s="28" t="inlineStr">
-        <is>
-          <t>€24.2k</t>
-        </is>
-      </c>
-      <c r="I34" s="28" t="inlineStr">
-        <is>
-          <t>€28.2k</t>
-        </is>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
-        <is>
-          <t>€34.2k</t>
-        </is>
-      </c>
-      <c r="K34" s="28" t="inlineStr">
-        <is>
-          <t>€34.2k</t>
-        </is>
-      </c>
-      <c r="L34" s="26" t="inlineStr">
-        <is>
-          <t>€186k total</t>
+      <c r="C33" s="28">
+        <f>(C27+C28)*$C$10+C31*$C$11</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>(D27+D28)*$C$10+D31*$C$11</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>(E27+E28)*$C$10+E31*$C$11</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>(F27+F28)*$C$10+F31*$C$11</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>(G27+G28)*$C$10+G31*$C$11</f>
+        <v/>
+      </c>
+      <c r="H33" s="28">
+        <f>(H27+H28)*$C$10+H31*$C$11</f>
+        <v/>
+      </c>
+      <c r="I33" s="28">
+        <f>(I27+I28)*$C$10+I31*$C$11</f>
+        <v/>
+      </c>
+      <c r="J33" s="28">
+        <f>(J27+J28)*$C$10+J31*$C$11</f>
+        <v/>
+      </c>
+      <c r="K33" s="28">
+        <f>(K27+K28)*$C$10+K31*$C$11</f>
+        <v/>
+      </c>
+      <c r="L33" s="27">
+        <f>SUM(C33:K33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>DEAL FLOW (edit these)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>DEAL FLOW</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>from AE capacity</t>
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr"/>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="inlineStr"/>
-      <c r="C37" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H37" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I37" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L37" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  capacity guide</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C37" s="50">
+        <f>ROUND(C30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="D37" s="50">
+        <f>ROUND(D30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="E37" s="50">
+        <f>ROUND(E30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="50">
+        <f>ROUND(F30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="50">
+        <f>ROUND(G30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="50">
+        <f>ROUND(H30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="I37" s="50">
+        <f>ROUND(I30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="50">
+        <f>ROUND(J30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="K37" s="50">
+        <f>ROUND(K30*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="L37" s="50">
+        <f>SUM(C37:K37)</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -3641,35 +3771,36 @@
           <t>€15K ARR</t>
         </is>
       </c>
-      <c r="C38" s="28" t="n">
+      <c r="C38" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="28" t="n">
+      <c r="D38" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="28" t="n">
+      <c r="E38" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="28" t="n">
+      <c r="I38" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="K38" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="K38" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="L38" s="26" t="n">
-        <v>37</v>
+      <c r="L38" s="28">
+        <f>SUM(C38:K38)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -3683,35 +3814,36 @@
           <t>€50K ARR</t>
         </is>
       </c>
-      <c r="C39" s="28" t="n">
+      <c r="C39" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="28" t="n">
+      <c r="D39" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="28" t="n">
+      <c r="E39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="28" t="n">
+      <c r="F39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="28" t="n">
+      <c r="G39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="28" t="n">
+      <c r="H39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="28" t="n">
+      <c r="I39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="28" t="n">
+      <c r="J39" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="K39" s="28" t="n">
+      <c r="K39" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="L39" s="26" t="n">
-        <v>9</v>
+      <c r="L39" s="28">
+        <f>SUM(C39:K39)</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -3725,83 +3857,89 @@
           <t>€100K ARR</t>
         </is>
       </c>
-      <c r="C40" s="28" t="n">
+      <c r="C40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="28" t="n">
+      <c r="D40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="28" t="n">
+      <c r="E40" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="28" t="n">
+      <c r="F40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="28" t="n">
+      <c r="H40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="28" t="n">
+      <c r="I40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="28" t="n">
+      <c r="J40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="28" t="n">
+      <c r="K40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="K40" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="26" t="n">
-        <v>6</v>
+      <c r="L40" s="28">
+        <f>SUM(C40:K40)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Total deals closing</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>52</v>
+          <t>Total deals</t>
+        </is>
+      </c>
+      <c r="C41" s="27">
+        <f>C38+C39+C40</f>
+        <v/>
+      </c>
+      <c r="D41" s="27">
+        <f>D38+D39+D40</f>
+        <v/>
+      </c>
+      <c r="E41" s="27">
+        <f>E38+E39+E40</f>
+        <v/>
+      </c>
+      <c r="F41" s="27">
+        <f>F38+F39+F40</f>
+        <v/>
+      </c>
+      <c r="G41" s="27">
+        <f>G38+G39+G40</f>
+        <v/>
+      </c>
+      <c r="H41" s="27">
+        <f>H38+H39+H40</f>
+        <v/>
+      </c>
+      <c r="I41" s="27">
+        <f>I38+I39+I40</f>
+        <v/>
+      </c>
+      <c r="J41" s="27">
+        <f>J38+J39+J40</f>
+        <v/>
+      </c>
+      <c r="K41" s="27">
+        <f>K38+K39+K40</f>
+        <v/>
+      </c>
+      <c r="L41" s="27">
+        <f>SUM(C41:K41)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
+          <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
@@ -3814,60 +3952,50 @@
       <c r="B44" s="22" t="inlineStr"/>
       <c r="C44" s="22" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D44" s="22" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="E44" s="22" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F44" s="22" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="G44" s="22" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="H44" s="22" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="K44" s="22" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="L44" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M44" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N44" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3876,1178 +4004,1407 @@
     <row r="45">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>Deals closing</t>
+          <t>Meetings needed /mo</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C45" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H45" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I45" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K45" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L45" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="M45" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="N45" s="29" t="n">
-        <v>52</v>
+          <t>deals ÷ close %</t>
+        </is>
+      </c>
+      <c r="C45" s="28">
+        <f>IF($C$7&gt;0,CEILING(C41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="D45" s="28">
+        <f>IF($C$7&gt;0,CEILING(D41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="E45" s="28">
+        <f>IF($C$7&gt;0,CEILING(E41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="28">
+        <f>IF($C$7&gt;0,CEILING(F41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="G45" s="28">
+        <f>IF($C$7&gt;0,CEILING(G41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="28">
+        <f>IF($C$7&gt;0,CEILING(H41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="I45" s="28">
+        <f>IF($C$7&gt;0,CEILING(I41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="28">
+        <f>IF($C$7&gt;0,CEILING(J41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="K45" s="28">
+        <f>IF($C$7&gt;0,CEILING(K41/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="L45" s="27">
+        <f>SUM(C45:K45)</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="inlineStr">
         <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C46" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" s="43" t="n">
-        <v>40</v>
-      </c>
-      <c r="F46" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G46" s="43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H46" s="43" t="n">
-        <v>70</v>
-      </c>
-      <c r="I46" s="43" t="n">
-        <v>70</v>
-      </c>
-      <c r="J46" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="K46" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="L46" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M46" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="44" t="n">
-        <v>520</v>
+          <t>From SMB BDR (free)</t>
+        </is>
+      </c>
+      <c r="C46" s="51">
+        <f>MIN($C$9,C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="51">
+        <f>MIN($C$9,D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="51">
+        <f>MIN($C$9,E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="51">
+        <f>MIN($C$9,F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="51">
+        <f>MIN($C$9,G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="51">
+        <f>MIN($C$9,H45)</f>
+        <v/>
+      </c>
+      <c r="I46" s="51">
+        <f>MIN($C$9,I45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="51">
+        <f>MIN($C$9,J45)</f>
+        <v/>
+      </c>
+      <c r="K46" s="51">
+        <f>MIN($C$9,K45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="51">
+        <f>SUM(C46:K46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>From dedicated BDRs</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>needed /mo</t>
+        </is>
+      </c>
+      <c r="C47" s="28">
+        <f>MAX(0,C45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="D47" s="28">
+        <f>MAX(0,D45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="E47" s="28">
+        <f>MAX(0,E45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="F47" s="28">
+        <f>MAX(0,F45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="G47" s="28">
+        <f>MAX(0,G45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="H47" s="28">
+        <f>MAX(0,H45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="I47" s="28">
+        <f>MAX(0,I45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="J47" s="28">
+        <f>MAX(0,J45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="K47" s="28">
+        <f>MAX(0,K45-$C$9)</f>
+        <v/>
+      </c>
+      <c r="L47" s="27">
+        <f>SUM(C47:K47)</f>
+        <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>BDRs needed (peak)</t>
+        </is>
+      </c>
+      <c r="C48" s="27">
+        <f>IF($C$8&gt;0,CEILING(MAX(C47:K47)/$C$8,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>ARR WATERFALL</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr"/>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="B51" s="22" t="inlineStr"/>
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D49" s="22" t="inlineStr">
+      <c r="D51" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F51" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
+      <c r="G51" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H49" s="22" t="inlineStr">
+      <c r="H51" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I49" s="22" t="inlineStr">
+      <c r="I51" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J49" s="22" t="inlineStr">
+      <c r="J51" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K49" s="22" t="inlineStr">
+      <c r="K51" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L49" s="22" t="inlineStr">
+      <c r="L51" s="22" t="inlineStr">
         <is>
           <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C50" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D50" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="E50" s="30" t="inlineStr">
-        <is>
-          <t>€95k</t>
-        </is>
-      </c>
-      <c r="F50" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="G50" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="H50" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="I50" s="30" t="inlineStr">
-        <is>
-          <t>€225k</t>
-        </is>
-      </c>
-      <c r="J50" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="K50" s="30" t="inlineStr">
-        <is>
-          <t>€305k</t>
-        </is>
-      </c>
-      <c r="L50" s="29" t="inlineStr">
-        <is>
-          <t>€1.60M</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B51" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D51" s="31" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>€125k</t>
-        </is>
-      </c>
-      <c r="F51" s="31" t="inlineStr">
-        <is>
-          <t>€335k</t>
-        </is>
-      </c>
-      <c r="G51" s="31" t="inlineStr">
-        <is>
-          <t>€560k</t>
-        </is>
-      </c>
-      <c r="H51" s="31" t="inlineStr">
-        <is>
-          <t>€785k</t>
-        </is>
-      </c>
-      <c r="I51" s="31" t="inlineStr">
-        <is>
-          <t>€1.01M</t>
-        </is>
-      </c>
-      <c r="J51" s="31" t="inlineStr">
-        <is>
-          <t>€1.30M</t>
-        </is>
-      </c>
-      <c r="K51" s="31" t="inlineStr">
-        <is>
-          <t>€1.60M</t>
-        </is>
-      </c>
-      <c r="L51" s="32" t="inlineStr">
-        <is>
-          <t>€1.60M</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="23" t="inlineStr">
         <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="K52" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="L52" s="42" t="inlineStr">
-        <is>
-          <t>+€105k</t>
-        </is>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C52" s="52">
+        <f>C38*$C$4+C39*$C$5+C40*$C$6</f>
+        <v/>
+      </c>
+      <c r="D52" s="52">
+        <f>D38*$C$4+D39*$C$5+D40*$C$6</f>
+        <v/>
+      </c>
+      <c r="E52" s="52">
+        <f>E38*$C$4+E39*$C$5+E40*$C$6</f>
+        <v/>
+      </c>
+      <c r="F52" s="52">
+        <f>F38*$C$4+F39*$C$5+F40*$C$6</f>
+        <v/>
+      </c>
+      <c r="G52" s="52">
+        <f>G38*$C$4+G39*$C$5+G40*$C$6</f>
+        <v/>
+      </c>
+      <c r="H52" s="52">
+        <f>H38*$C$4+H39*$C$5+H40*$C$6</f>
+        <v/>
+      </c>
+      <c r="I52" s="52">
+        <f>I38*$C$4+I39*$C$5+I40*$C$6</f>
+        <v/>
+      </c>
+      <c r="J52" s="52">
+        <f>J38*$C$4+J39*$C$5+J40*$C$6</f>
+        <v/>
+      </c>
+      <c r="K52" s="52">
+        <f>K38*$C$4+K39*$C$5+K40*$C$6</f>
+        <v/>
+      </c>
+      <c r="L52" s="27">
+        <f>SUM(C52:K52)</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="23" t="inlineStr">
         <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B53" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C53" s="27">
+        <f>C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="27">
+        <f>C53+D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="27">
+        <f>D53+E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="27">
+        <f>E53+F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="27">
+        <f>F53+G52</f>
+        <v/>
+      </c>
+      <c r="H53" s="27">
+        <f>G53+H52</f>
+        <v/>
+      </c>
+      <c r="I53" s="27">
+        <f>H53+I52</f>
+        <v/>
+      </c>
+      <c r="J53" s="27">
+        <f>I53+J52</f>
+        <v/>
+      </c>
+      <c r="K53" s="27">
+        <f>J53+K52</f>
+        <v/>
+      </c>
+      <c r="L53" s="27">
+        <f>K53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>pilot conv. upside</t>
+        </is>
+      </c>
+      <c r="C54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="54">
+        <f>ROUND(C38*$C$15,0)*($C$5-$C$4)+ROUND(C38*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="I54" s="54">
+        <f>ROUND(D38*$C$15,0)*($C$5-$C$4)+ROUND(D38*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="J54" s="54">
+        <f>ROUND(E38*$C$15,0)*($C$5-$C$4)+ROUND(E38*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="K54" s="54">
+        <f>ROUND(F38*$C$15,0)*($C$5-$C$4)+ROUND(F38*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="L54" s="38">
+        <f>SUM(C54:K54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
           <t>Total ARR</t>
         </is>
       </c>
-      <c r="C53" s="35" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D53" s="35" t="inlineStr">
-        <is>
-          <t>€30k</t>
-        </is>
-      </c>
-      <c r="E53" s="35" t="inlineStr">
-        <is>
-          <t>€125k</t>
-        </is>
-      </c>
-      <c r="F53" s="35" t="inlineStr">
-        <is>
-          <t>€335k</t>
-        </is>
-      </c>
-      <c r="G53" s="35" t="inlineStr">
-        <is>
-          <t>€560k</t>
-        </is>
-      </c>
-      <c r="H53" s="35" t="inlineStr">
-        <is>
-          <t>€785k</t>
-        </is>
-      </c>
-      <c r="I53" s="35" t="inlineStr">
-        <is>
-          <t>€1.01M</t>
-        </is>
-      </c>
-      <c r="J53" s="35" t="inlineStr">
-        <is>
-          <t>€1.33M</t>
-        </is>
-      </c>
-      <c r="K53" s="35" t="inlineStr">
-        <is>
-          <t>€1.71M</t>
-        </is>
-      </c>
-      <c r="L53" s="36" t="inlineStr">
-        <is>
-          <t>€1.71M</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>BDR FUNNEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="18" t="inlineStr">
-        <is>
-          <t>52 deals ÷ 10% = 520 meetings over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="18">
-        <f> 58/mo − 15 from SMB BDRs = 43 from dedicated BDRs</f>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>incl. expansion</t>
+        </is>
+      </c>
+      <c r="C55" s="35">
+        <f>C52+C54</f>
+        <v/>
+      </c>
+      <c r="D55" s="35">
+        <f>C55+D52+D54</f>
+        <v/>
+      </c>
+      <c r="E55" s="35">
+        <f>D55+E52+E54</f>
+        <v/>
+      </c>
+      <c r="F55" s="35">
+        <f>E55+F52+F54</f>
+        <v/>
+      </c>
+      <c r="G55" s="35">
+        <f>F55+G52+G54</f>
+        <v/>
+      </c>
+      <c r="H55" s="35">
+        <f>G55+H52+H54</f>
+        <v/>
+      </c>
+      <c r="I55" s="35">
+        <f>H55+I52+I54</f>
+        <v/>
+      </c>
+      <c r="J55" s="35">
+        <f>I55+J52+J54</f>
+        <v/>
+      </c>
+      <c r="K55" s="35">
+        <f>J55+K52+K54</f>
+        <v/>
+      </c>
+      <c r="L55" s="35">
+        <f>K55</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="37" t="inlineStr">
-        <is>
-          <t>43/mo ÷ 15/BDR = 3 dedicated MM BDRs needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>SCENARIO 2: PUSH</t>
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>Hit €2M — staggered hiring + May whale</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="inlineStr">
+        <is>
+          <t>Victor FT Jun. New AEs: Jun/Aug/Oct. May large deal. SMB→MM switch optional (Aug). Risk: MEDIUM.</t>
+        </is>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="19" t="inlineStr">
-        <is>
-          <t>Hit €2M — staggered hiring, one whale in the bag</t>
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>HEADCOUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr"/>
+      <c r="B63" s="22" t="inlineStr"/>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G63" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J63" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K63" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L63" s="22" t="inlineStr">
+        <is>
+          <t>Peak</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>NARRATIVE</t>
-        </is>
+      <c r="A64" s="23" t="inlineStr">
+        <is>
+          <t>AEs (ramped)</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>no ramp</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D64" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E64" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F64" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G64" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H64" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I64" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J64" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K64" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L64" s="28">
+        <f>MAX(C64:K64)</f>
+        <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="inlineStr">
-        <is>
-          <t>The push scenario targets €2M new deal ARR. Victor goes full-time in June. First new AE joins in June, a second in August, a third in October. Martijn increases to 0.5 FTE in August. A large deal already in advanced pipeline closes in May (€100K) — this anchors Q2.</t>
-        </is>
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>AEs (new hires)</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L65" s="28">
+        <f>MAX(C65:K65)</f>
+        <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="inlineStr">
-        <is>
-          <t>Optional lever: depending on AE hiring quality and skillset, we may switch one SMB AE to MM in August. This adds 1.0 FTE at full productivity (no ramp needed) and could reduce the need for the October new hire. Decision point: end of July based on Q3 pipeline quality.</t>
-        </is>
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  added this month</t>
+        </is>
+      </c>
+      <c r="C66" s="50">
+        <f>MAX(0,C65)</f>
+        <v/>
+      </c>
+      <c r="D66" s="50">
+        <f>MAX(0,D65-C65)</f>
+        <v/>
+      </c>
+      <c r="E66" s="50">
+        <f>MAX(0,E65-D65)</f>
+        <v/>
+      </c>
+      <c r="F66" s="50">
+        <f>MAX(0,F65-E65)</f>
+        <v/>
+      </c>
+      <c r="G66" s="50">
+        <f>MAX(0,G65-F65)</f>
+        <v/>
+      </c>
+      <c r="H66" s="50">
+        <f>MAX(0,H65-G65)</f>
+        <v/>
+      </c>
+      <c r="I66" s="50">
+        <f>MAX(0,I65-H65)</f>
+        <v/>
+      </c>
+      <c r="J66" s="50">
+        <f>MAX(0,J65-I65)</f>
+        <v/>
+      </c>
+      <c r="K66" s="50">
+        <f>MAX(0,K65-J65)</f>
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="21" t="inlineStr">
-        <is>
-          <t>Risk profile: MEDIUM. Monthly burn peaks at ~€38K. The staggered hiring gives exit ramps. If the June hire underperforms, we delay August. If close rates hold at 10%, we land at ~€2.1M. Expansion from pilot conversions adds upside. The SMB switch lever is insurance — if we use it, we can skip the October hire and still hit target.</t>
-        </is>
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>Effective AEs</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C67" s="28">
+        <f>C64+C66*$C$12</f>
+        <v/>
+      </c>
+      <c r="D67" s="28">
+        <f>D64+D66*$C$12+C66*$C$13</f>
+        <v/>
+      </c>
+      <c r="E67" s="28">
+        <f>E64+E66*$C$12+D66*$C$13+SUM(C66:C66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="F67" s="28">
+        <f>F64+F66*$C$12+E66*$C$13+SUM(C66:D66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="G67" s="28">
+        <f>G64+G66*$C$12+F66*$C$13+SUM(C66:E66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="H67" s="28">
+        <f>H64+H66*$C$12+G66*$C$13+SUM(C66:F66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="I67" s="28">
+        <f>I64+I66*$C$12+H66*$C$13+SUM(C66:G66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="J67" s="28">
+        <f>J64+J66*$C$12+I66*$C$13+SUM(C66:H66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="K67" s="28">
+        <f>K64+K66*$C$12+J66*$C$13+SUM(C66:I66)*$C$14</f>
+        <v/>
+      </c>
+      <c r="L67" s="28">
+        <f>MAX(C67:K67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D68" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H68" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I68" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" s="28">
+        <f>MAX(C68:K68)</f>
+        <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="20" t="inlineStr">
-        <is>
-          <t>HEADCOUNT</t>
-        </is>
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C69" s="28">
+        <f>C64+C65+C68</f>
+        <v/>
+      </c>
+      <c r="D69" s="28">
+        <f>D64+D65+D68</f>
+        <v/>
+      </c>
+      <c r="E69" s="28">
+        <f>E64+E65+E68</f>
+        <v/>
+      </c>
+      <c r="F69" s="28">
+        <f>F64+F65+F68</f>
+        <v/>
+      </c>
+      <c r="G69" s="28">
+        <f>G64+G65+G68</f>
+        <v/>
+      </c>
+      <c r="H69" s="28">
+        <f>H64+H65+H68</f>
+        <v/>
+      </c>
+      <c r="I69" s="28">
+        <f>I64+I65+I68</f>
+        <v/>
+      </c>
+      <c r="J69" s="28">
+        <f>J64+J65+J68</f>
+        <v/>
+      </c>
+      <c r="K69" s="28">
+        <f>K64+K65+K68</f>
+        <v/>
+      </c>
+      <c r="L69" s="28">
+        <f>MAX(C69:K69)</f>
+        <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
-        <is>
-          <t>Ramped: Martijn 0.2→0.5 (Aug), Mossel 0.2, Victor 0.2→1.0 (Jun)</t>
-        </is>
-      </c>
-      <c r="F70" s="46" t="inlineStr">
-        <is>
-          <t>SMB→MM switch: Aug</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="22" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B71" s="22" t="inlineStr">
+      <c r="A70" s="23" t="inlineStr">
+        <is>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="C70" s="28">
+        <f>(C64+C65)*$C$10+C68*$C$11</f>
+        <v/>
+      </c>
+      <c r="D70" s="28">
+        <f>(D64+D65)*$C$10+D68*$C$11</f>
+        <v/>
+      </c>
+      <c r="E70" s="28">
+        <f>(E64+E65)*$C$10+E68*$C$11</f>
+        <v/>
+      </c>
+      <c r="F70" s="28">
+        <f>(F64+F65)*$C$10+F68*$C$11</f>
+        <v/>
+      </c>
+      <c r="G70" s="28">
+        <f>(G64+G65)*$C$10+G68*$C$11</f>
+        <v/>
+      </c>
+      <c r="H70" s="28">
+        <f>(H64+H65)*$C$10+H68*$C$11</f>
+        <v/>
+      </c>
+      <c r="I70" s="28">
+        <f>(I64+I65)*$C$10+I68*$C$11</f>
+        <v/>
+      </c>
+      <c r="J70" s="28">
+        <f>(J64+J65)*$C$10+J68*$C$11</f>
+        <v/>
+      </c>
+      <c r="K70" s="28">
+        <f>(K64+K65)*$C$10+K68*$C$11</f>
+        <v/>
+      </c>
+      <c r="L70" s="27">
+        <f>SUM(C70:K70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>DEAL FLOW (edit these)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C71" s="22" t="inlineStr">
+      <c r="B73" s="22" t="inlineStr"/>
+      <c r="C73" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D71" s="22" t="inlineStr">
+      <c r="D73" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E71" s="22" t="inlineStr">
+      <c r="E73" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F71" s="22" t="inlineStr">
+      <c r="F73" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G71" s="22" t="inlineStr">
+      <c r="G73" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H71" s="22" t="inlineStr">
+      <c r="H73" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I71" s="22" t="inlineStr">
+      <c r="I73" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J71" s="22" t="inlineStr">
+      <c r="J73" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K71" s="22" t="inlineStr">
+      <c r="K73" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L71" s="22" t="inlineStr">
-        <is>
-          <t>Peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="23" t="inlineStr">
-        <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>no ramp</t>
-        </is>
-      </c>
-      <c r="C72" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D72" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E72" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F72" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G72" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H72" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I72" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J72" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K72" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L72" s="26" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t>AEs (new hires)</t>
-        </is>
-      </c>
-      <c r="B73" s="24" t="inlineStr">
-        <is>
-          <t>with ramp</t>
-        </is>
-      </c>
-      <c r="C73" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H73" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K73" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" s="26" t="n">
-        <v>3</v>
+      <c r="L73" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
-        <is>
-          <t>Effective AEs</t>
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  capacity guide</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C74" s="27" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D74" s="27" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="E74" s="27" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="G74" s="27" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="H74" s="27" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="I74" s="27" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="J74" s="27" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="K74" s="27" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="L74" s="26" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C74" s="50">
+        <f>ROUND(C67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="D74" s="50">
+        <f>ROUND(D67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="E74" s="50">
+        <f>ROUND(E67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="F74" s="50">
+        <f>ROUND(F67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="G74" s="50">
+        <f>ROUND(G67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="H74" s="50">
+        <f>ROUND(H67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="I74" s="50">
+        <f>ROUND(I67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="J74" s="50">
+        <f>ROUND(J67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="K74" s="50">
+        <f>ROUND(K67*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="L74" s="50">
+        <f>SUM(C74:K74)</f>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>BDRs (dedicated)</t>
+          <t>Pilots</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>€15K ARR</t>
         </is>
       </c>
       <c r="C75" s="25" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D75" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E75" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" s="25" t="n">
         <v>3</v>
       </c>
       <c r="G75" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H75" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I75" s="25" t="n">
         <v>5</v>
       </c>
       <c r="J75" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="L75" s="26" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="L75" s="28">
+        <f>SUM(C75:K75)</f>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="23" t="inlineStr">
         <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C76" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D76" s="27" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="E76" s="27" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="G76" s="27" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="H76" s="27" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="I76" s="27" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="J76" s="27" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="K76" s="27" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="L76" s="26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>€50K ARR</t>
+        </is>
+      </c>
+      <c r="C76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" s="28">
+        <f>SUM(C76:K76)</f>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="23" t="inlineStr">
         <is>
-          <t>Monthly cost</t>
-        </is>
-      </c>
-      <c r="C77" s="28" t="inlineStr">
-        <is>
-          <t>€5.2k</t>
-        </is>
-      </c>
-      <c r="D77" s="28" t="inlineStr">
-        <is>
-          <t>€7.6k</t>
-        </is>
-      </c>
-      <c r="E77" s="28" t="inlineStr">
-        <is>
-          <t>€22.4k</t>
-        </is>
-      </c>
-      <c r="F77" s="28" t="inlineStr">
-        <is>
-          <t>€26.4k</t>
-        </is>
-      </c>
-      <c r="G77" s="28" t="inlineStr">
-        <is>
-          <t>€38.2k</t>
-        </is>
-      </c>
-      <c r="H77" s="28" t="inlineStr">
-        <is>
-          <t>€38.2k</t>
-        </is>
-      </c>
-      <c r="I77" s="28" t="inlineStr">
-        <is>
-          <t>€42.2k</t>
-        </is>
-      </c>
-      <c r="J77" s="28" t="inlineStr">
-        <is>
-          <t>€48.2k</t>
-        </is>
-      </c>
-      <c r="K77" s="28" t="inlineStr">
-        <is>
-          <t>€48.2k</t>
-        </is>
-      </c>
-      <c r="L77" s="26" t="inlineStr">
-        <is>
-          <t>€277k total</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>DEAL FLOW</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>from AE capacity</t>
-        </is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C77" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="28">
+        <f>SUM(C77:K77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t>Total deals</t>
+        </is>
+      </c>
+      <c r="C78" s="27">
+        <f>C75+C76+C77</f>
+        <v/>
+      </c>
+      <c r="D78" s="27">
+        <f>D75+D76+D77</f>
+        <v/>
+      </c>
+      <c r="E78" s="27">
+        <f>E75+E76+E77</f>
+        <v/>
+      </c>
+      <c r="F78" s="27">
+        <f>F75+F76+F77</f>
+        <v/>
+      </c>
+      <c r="G78" s="27">
+        <f>G75+G76+G77</f>
+        <v/>
+      </c>
+      <c r="H78" s="27">
+        <f>H75+H76+H77</f>
+        <v/>
+      </c>
+      <c r="I78" s="27">
+        <f>I75+I76+I77</f>
+        <v/>
+      </c>
+      <c r="J78" s="27">
+        <f>J75+J76+J77</f>
+        <v/>
+      </c>
+      <c r="K78" s="27">
+        <f>K75+K76+K77</f>
+        <v/>
+      </c>
+      <c r="L78" s="27">
+        <f>SUM(C78:K78)</f>
+        <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="22" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B80" s="22" t="inlineStr"/>
-      <c r="C80" s="22" t="inlineStr">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>BDR FUNNEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr"/>
+      <c r="C81" s="22" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D80" s="22" t="inlineStr">
+      <c r="D81" s="22" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="E80" s="22" t="inlineStr">
+      <c r="E81" s="22" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F80" s="22" t="inlineStr">
+      <c r="F81" s="22" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
+      <c r="G81" s="22" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="H80" s="22" t="inlineStr">
+      <c r="H81" s="22" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="I80" s="22" t="inlineStr">
+      <c r="I81" s="22" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="J80" s="22" t="inlineStr">
+      <c r="J81" s="22" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="K80" s="22" t="inlineStr">
+      <c r="K81" s="22" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="L80" s="22" t="inlineStr">
+      <c r="L81" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>Pilots</t>
-        </is>
-      </c>
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C81" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F81" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H81" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="I81" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="K81" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="L81" s="26" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Meetings needed /mo</t>
         </is>
       </c>
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>€50K ARR</t>
-        </is>
-      </c>
-      <c r="C82" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H82" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I82" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K82" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="26" t="n">
-        <v>12</v>
+          <t>deals ÷ close %</t>
+        </is>
+      </c>
+      <c r="C82" s="28">
+        <f>IF($C$7&gt;0,CEILING(C78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="D82" s="28">
+        <f>IF($C$7&gt;0,CEILING(D78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="E82" s="28">
+        <f>IF($C$7&gt;0,CEILING(E78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="F82" s="28">
+        <f>IF($C$7&gt;0,CEILING(F78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="G82" s="28">
+        <f>IF($C$7&gt;0,CEILING(G78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="H82" s="28">
+        <f>IF($C$7&gt;0,CEILING(H78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="I82" s="28">
+        <f>IF($C$7&gt;0,CEILING(I78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="28">
+        <f>IF($C$7&gt;0,CEILING(J78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="K82" s="28">
+        <f>IF($C$7&gt;0,CEILING(K78/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="L82" s="27">
+        <f>SUM(C82:K82)</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="B83" s="24" t="inlineStr">
-        <is>
-          <t>€100K ARR</t>
-        </is>
-      </c>
-      <c r="C83" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="45" t="inlineStr">
-        <is>
-          <t>1*</t>
-        </is>
-      </c>
-      <c r="E83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="26" t="n">
-        <v>8</v>
+          <t>From SMB BDR (free)</t>
+        </is>
+      </c>
+      <c r="C83" s="51">
+        <f>MIN($C$9,C82)</f>
+        <v/>
+      </c>
+      <c r="D83" s="51">
+        <f>MIN($C$9,D82)</f>
+        <v/>
+      </c>
+      <c r="E83" s="51">
+        <f>MIN($C$9,E82)</f>
+        <v/>
+      </c>
+      <c r="F83" s="51">
+        <f>MIN($C$9,F82)</f>
+        <v/>
+      </c>
+      <c r="G83" s="51">
+        <f>MIN($C$9,G82)</f>
+        <v/>
+      </c>
+      <c r="H83" s="51">
+        <f>MIN($C$9,H82)</f>
+        <v/>
+      </c>
+      <c r="I83" s="51">
+        <f>MIN($C$9,I82)</f>
+        <v/>
+      </c>
+      <c r="J83" s="51">
+        <f>MIN($C$9,J82)</f>
+        <v/>
+      </c>
+      <c r="K83" s="51">
+        <f>MIN($C$9,K82)</f>
+        <v/>
+      </c>
+      <c r="L83" s="51">
+        <f>SUM(C83:K83)</f>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t>Total deals closing</t>
-        </is>
-      </c>
-      <c r="C84" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="F84" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="G84" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="H84" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="I84" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="K84" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="L84" s="26" t="n">
-        <v>67</v>
+          <t>From dedicated BDRs</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>needed /mo</t>
+        </is>
+      </c>
+      <c r="C84" s="28">
+        <f>MAX(0,C82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="D84" s="28">
+        <f>MAX(0,D82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="E84" s="28">
+        <f>MAX(0,E82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="F84" s="28">
+        <f>MAX(0,F82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="G84" s="28">
+        <f>MAX(0,G82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="H84" s="28">
+        <f>MAX(0,H82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="I84" s="28">
+        <f>MAX(0,I82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="J84" s="28">
+        <f>MAX(0,J82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="K84" s="28">
+        <f>MAX(0,K82-$C$9)</f>
+        <v/>
+      </c>
+      <c r="L84" s="27">
+        <f>SUM(C84:K84)</f>
+        <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="inlineStr">
-        <is>
-          <t>* = deal in pipeline (not from capacity)</t>
-        </is>
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>BDRs needed (peak)</t>
+        </is>
+      </c>
+      <c r="C85" s="27">
+        <f>IF($C$8&gt;0,CEILING(MAX(C84:K84)/$C$8,1),0)</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
+          <t>ARR WATERFALL</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr"/>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="E88" s="22" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F88" s="22" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="G88" s="22" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="H88" s="22" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="I88" s="22" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="J88" s="22" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="K88" s="22" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="L88" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M88" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N88" s="22" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -5056,1660 +5413,1387 @@
     <row r="89">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C89" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H89" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I89" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="J89" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="K89" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="L89" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="M89" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="N89" s="29" t="n">
-        <v>67</v>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C89" s="52">
+        <f>C75*$C$4+C76*$C$5+C77*$C$6</f>
+        <v/>
+      </c>
+      <c r="D89" s="52">
+        <f>D75*$C$4+D76*$C$5+D77*$C$6</f>
+        <v/>
+      </c>
+      <c r="E89" s="52">
+        <f>E75*$C$4+E76*$C$5+E77*$C$6</f>
+        <v/>
+      </c>
+      <c r="F89" s="52">
+        <f>F75*$C$4+F76*$C$5+F77*$C$6</f>
+        <v/>
+      </c>
+      <c r="G89" s="52">
+        <f>G75*$C$4+G76*$C$5+G77*$C$6</f>
+        <v/>
+      </c>
+      <c r="H89" s="52">
+        <f>H75*$C$4+H76*$C$5+H77*$C$6</f>
+        <v/>
+      </c>
+      <c r="I89" s="52">
+        <f>I75*$C$4+I76*$C$5+I77*$C$6</f>
+        <v/>
+      </c>
+      <c r="J89" s="52">
+        <f>J75*$C$4+J76*$C$5+J77*$C$6</f>
+        <v/>
+      </c>
+      <c r="K89" s="52">
+        <f>K75*$C$4+K76*$C$5+K77*$C$6</f>
+        <v/>
+      </c>
+      <c r="L89" s="27">
+        <f>SUM(C89:K89)</f>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="inlineStr">
         <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B90" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C90" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D90" s="43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E90" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F90" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G90" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="H90" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="I90" s="43" t="n">
-        <v>100</v>
-      </c>
-      <c r="J90" s="43" t="n">
-        <v>110</v>
-      </c>
-      <c r="K90" s="43" t="n">
-        <v>120</v>
-      </c>
-      <c r="L90" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M90" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" s="44" t="n">
-        <v>670</v>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B90" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C90" s="27">
+        <f>C89</f>
+        <v/>
+      </c>
+      <c r="D90" s="27">
+        <f>C90+D89</f>
+        <v/>
+      </c>
+      <c r="E90" s="27">
+        <f>D90+E89</f>
+        <v/>
+      </c>
+      <c r="F90" s="27">
+        <f>E90+F89</f>
+        <v/>
+      </c>
+      <c r="G90" s="27">
+        <f>F90+G89</f>
+        <v/>
+      </c>
+      <c r="H90" s="27">
+        <f>G90+H89</f>
+        <v/>
+      </c>
+      <c r="I90" s="27">
+        <f>H90+I89</f>
+        <v/>
+      </c>
+      <c r="J90" s="27">
+        <f>I90+J89</f>
+        <v/>
+      </c>
+      <c r="K90" s="27">
+        <f>J90+K89</f>
+        <v/>
+      </c>
+      <c r="L90" s="27">
+        <f>K90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>pilot conv. upside</t>
+        </is>
+      </c>
+      <c r="C91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="54">
+        <f>ROUND(C75*$C$15,0)*($C$5-$C$4)+ROUND(C75*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="I91" s="54">
+        <f>ROUND(D75*$C$15,0)*($C$5-$C$4)+ROUND(D75*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="J91" s="54">
+        <f>ROUND(E75*$C$15,0)*($C$5-$C$4)+ROUND(E75*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="K91" s="54">
+        <f>ROUND(F75*$C$15,0)*($C$5-$C$4)+ROUND(F75*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="L91" s="38">
+        <f>SUM(C91:K91)</f>
+        <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B93" s="22" t="inlineStr"/>
-      <c r="C93" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D93" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E93" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F93" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G93" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H93" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I93" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J93" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K93" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L93" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C94" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D94" s="30" t="inlineStr">
-        <is>
-          <t>€115k</t>
-        </is>
-      </c>
-      <c r="E94" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="F94" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="G94" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="H94" s="30" t="inlineStr">
-        <is>
-          <t>€305k</t>
-        </is>
-      </c>
-      <c r="I94" s="30" t="inlineStr">
-        <is>
-          <t>€305k</t>
-        </is>
-      </c>
-      <c r="J94" s="30" t="inlineStr">
-        <is>
-          <t>€320k</t>
-        </is>
-      </c>
-      <c r="K94" s="30" t="inlineStr">
-        <is>
-          <t>€335k</t>
-        </is>
-      </c>
-      <c r="L94" s="29" t="inlineStr">
-        <is>
-          <t>€2.10M</t>
-        </is>
+      <c r="A92" s="23" t="inlineStr">
+        <is>
+          <t>Total ARR</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>incl. expansion</t>
+        </is>
+      </c>
+      <c r="C92" s="35">
+        <f>C89+C91</f>
+        <v/>
+      </c>
+      <c r="D92" s="35">
+        <f>C92+D89+D91</f>
+        <v/>
+      </c>
+      <c r="E92" s="35">
+        <f>D92+E89+E91</f>
+        <v/>
+      </c>
+      <c r="F92" s="35">
+        <f>E92+F89+F91</f>
+        <v/>
+      </c>
+      <c r="G92" s="35">
+        <f>F92+G89+G91</f>
+        <v/>
+      </c>
+      <c r="H92" s="35">
+        <f>G92+H89+H91</f>
+        <v/>
+      </c>
+      <c r="I92" s="35">
+        <f>H92+I89+I91</f>
+        <v/>
+      </c>
+      <c r="J92" s="35">
+        <f>I92+J89+J91</f>
+        <v/>
+      </c>
+      <c r="K92" s="35">
+        <f>J92+K89+K91</f>
+        <v/>
+      </c>
+      <c r="L92" s="35">
+        <f>K92</f>
+        <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B95" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C95" s="38" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D95" s="38" t="inlineStr">
-        <is>
-          <t>€130k</t>
-        </is>
-      </c>
-      <c r="E95" s="38" t="inlineStr">
-        <is>
-          <t>€340k</t>
-        </is>
-      </c>
-      <c r="F95" s="38" t="inlineStr">
-        <is>
-          <t>€550k</t>
-        </is>
-      </c>
-      <c r="G95" s="38" t="inlineStr">
-        <is>
-          <t>€840k</t>
-        </is>
-      </c>
-      <c r="H95" s="38" t="inlineStr">
-        <is>
-          <t>€1.15M</t>
-        </is>
-      </c>
-      <c r="I95" s="38" t="inlineStr">
-        <is>
-          <t>€1.45M</t>
-        </is>
-      </c>
-      <c r="J95" s="38" t="inlineStr">
-        <is>
-          <t>€1.77M</t>
-        </is>
-      </c>
-      <c r="K95" s="38" t="inlineStr">
-        <is>
-          <t>€2.10M</t>
-        </is>
-      </c>
-      <c r="L95" s="41" t="inlineStr">
-        <is>
-          <t>€2.10M</t>
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>SCENARIO 3: HYPER-PUSH</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="23" t="inlineStr">
-        <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B96" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="K96" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="L96" s="42" t="inlineStr">
-        <is>
-          <t>+€140k</t>
+      <c r="A96" s="19" t="inlineStr">
+        <is>
+          <t>Build the €3M machine</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="23" t="inlineStr">
-        <is>
-          <t>Total ARR</t>
-        </is>
-      </c>
-      <c r="C97" s="35" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D97" s="35" t="inlineStr">
-        <is>
-          <t>€130k</t>
-        </is>
-      </c>
-      <c r="E97" s="35" t="inlineStr">
-        <is>
-          <t>€340k</t>
-        </is>
-      </c>
-      <c r="F97" s="35" t="inlineStr">
-        <is>
-          <t>€550k</t>
-        </is>
-      </c>
-      <c r="G97" s="35" t="inlineStr">
-        <is>
-          <t>€840k</t>
-        </is>
-      </c>
-      <c r="H97" s="35" t="inlineStr">
-        <is>
-          <t>€1.15M</t>
-        </is>
-      </c>
-      <c r="I97" s="35" t="inlineStr">
-        <is>
-          <t>€1.45M</t>
-        </is>
-      </c>
-      <c r="J97" s="35" t="inlineStr">
-        <is>
-          <t>€1.84M</t>
-        </is>
-      </c>
-      <c r="K97" s="35" t="inlineStr">
-        <is>
-          <t>€2.25M</t>
-        </is>
-      </c>
-      <c r="L97" s="36" t="inlineStr">
-        <is>
-          <t>€2.25M</t>
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>Victor FT May. New AEs: Jun/Jul(2)/Sep(2)/Nov. SMB switch Aug. Needs team lead by Aug. Risk: HIGH.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>BDR FUNNEL</t>
+          <t>HEADCOUNT</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="18" t="inlineStr">
-        <is>
-          <t>67 deals ÷ 10% = 670 meetings over 9 months</t>
+      <c r="A100" s="22" t="inlineStr"/>
+      <c r="B100" s="22" t="inlineStr"/>
+      <c r="C100" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E100" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G100" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J100" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K100" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L100" s="22" t="inlineStr">
+        <is>
+          <t>Peak</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="18">
-        <f> 75/mo − 15 from SMB BDRs = 60 from dedicated BDRs</f>
+      <c r="A101" s="23" t="inlineStr">
+        <is>
+          <t>AEs (ramped)</t>
+        </is>
+      </c>
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>no ramp</t>
+        </is>
+      </c>
+      <c r="C101" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D101" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E101" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F101" s="25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G101" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H101" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I101" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J101" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K101" s="25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L101" s="28">
+        <f>MAX(C101:K101)</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="37" t="inlineStr">
-        <is>
-          <t>60/mo ÷ 15/BDR = 4 dedicated MM BDRs needed</t>
-        </is>
+      <c r="A102" s="23" t="inlineStr">
+        <is>
+          <t>AEs (new hires)</t>
+        </is>
+      </c>
+      <c r="B102" s="24" t="inlineStr">
+        <is>
+          <t>cumulative</t>
+        </is>
+      </c>
+      <c r="C102" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I102" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J102" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="28">
+        <f>MAX(C102:K102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  added this month</t>
+        </is>
+      </c>
+      <c r="C103" s="50">
+        <f>MAX(0,C102)</f>
+        <v/>
+      </c>
+      <c r="D103" s="50">
+        <f>MAX(0,D102-C102)</f>
+        <v/>
+      </c>
+      <c r="E103" s="50">
+        <f>MAX(0,E102-D102)</f>
+        <v/>
+      </c>
+      <c r="F103" s="50">
+        <f>MAX(0,F102-E102)</f>
+        <v/>
+      </c>
+      <c r="G103" s="50">
+        <f>MAX(0,G102-F102)</f>
+        <v/>
+      </c>
+      <c r="H103" s="50">
+        <f>MAX(0,H102-G102)</f>
+        <v/>
+      </c>
+      <c r="I103" s="50">
+        <f>MAX(0,I102-H102)</f>
+        <v/>
+      </c>
+      <c r="J103" s="50">
+        <f>MAX(0,J102-I102)</f>
+        <v/>
+      </c>
+      <c r="K103" s="50">
+        <f>MAX(0,K102-J102)</f>
+        <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="47" t="inlineStr">
-        <is>
-          <t>IF SMB→MM SWITCH ACTIVATED (Aug)</t>
-        </is>
+      <c r="A104" s="23" t="inlineStr">
+        <is>
+          <t>Effective AEs</t>
+        </is>
+      </c>
+      <c r="B104" s="24" t="inlineStr">
+        <is>
+          <t>incl. ramp</t>
+        </is>
+      </c>
+      <c r="C104" s="28">
+        <f>C101+C103*$C$12</f>
+        <v/>
+      </c>
+      <c r="D104" s="28">
+        <f>D101+D103*$C$12+C103*$C$13</f>
+        <v/>
+      </c>
+      <c r="E104" s="28">
+        <f>E101+E103*$C$12+D103*$C$13+SUM(C103:C103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="F104" s="28">
+        <f>F101+F103*$C$12+E103*$C$13+SUM(C103:D103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="G104" s="28">
+        <f>G101+G103*$C$12+F103*$C$13+SUM(C103:E103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="H104" s="28">
+        <f>H101+H103*$C$12+G103*$C$13+SUM(C103:F103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="I104" s="28">
+        <f>I101+I103*$C$12+H103*$C$13+SUM(C103:G103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="J104" s="28">
+        <f>J101+J103*$C$12+I103*$C$13+SUM(C103:H103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="K104" s="28">
+        <f>K101+K103*$C$12+J103*$C$13+SUM(C103:I103)*$C$14</f>
+        <v/>
+      </c>
+      <c r="L104" s="28">
+        <f>MAX(C104:K104)</f>
+        <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="18" t="inlineStr">
-        <is>
-          <t>Drops Oct new hire. New deal ARR: €2.51M | Total: €2.65M | Saves 1 new hire.</t>
-        </is>
+      <c r="A105" s="23" t="inlineStr">
+        <is>
+          <t>BDRs (dedicated)</t>
+        </is>
+      </c>
+      <c r="B105" s="24" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+      <c r="C105" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D105" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H105" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J105" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K105" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" s="28">
+        <f>MAX(C105:K105)</f>
+        <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="24" t="inlineStr">
-        <is>
-          <t>Effective AEs: ['0.6', '0.6', '1.9', '2.1', '4.2', '4.5', '4.7', '4.7', '4.7']</t>
-        </is>
+      <c r="A106" s="23" t="inlineStr">
+        <is>
+          <t>Total headcount</t>
+        </is>
+      </c>
+      <c r="C106" s="28">
+        <f>C101+C102+C105</f>
+        <v/>
+      </c>
+      <c r="D106" s="28">
+        <f>D101+D102+D105</f>
+        <v/>
+      </c>
+      <c r="E106" s="28">
+        <f>E101+E102+E105</f>
+        <v/>
+      </c>
+      <c r="F106" s="28">
+        <f>F101+F102+F105</f>
+        <v/>
+      </c>
+      <c r="G106" s="28">
+        <f>G101+G102+G105</f>
+        <v/>
+      </c>
+      <c r="H106" s="28">
+        <f>H101+H102+H105</f>
+        <v/>
+      </c>
+      <c r="I106" s="28">
+        <f>I101+I102+I105</f>
+        <v/>
+      </c>
+      <c r="J106" s="28">
+        <f>J101+J102+J105</f>
+        <v/>
+      </c>
+      <c r="K106" s="28">
+        <f>K101+K102+K105</f>
+        <v/>
+      </c>
+      <c r="L106" s="28">
+        <f>MAX(C106:K106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="C107" s="28">
+        <f>(C101+C102)*$C$10+C105*$C$11</f>
+        <v/>
+      </c>
+      <c r="D107" s="28">
+        <f>(D101+D102)*$C$10+D105*$C$11</f>
+        <v/>
+      </c>
+      <c r="E107" s="28">
+        <f>(E101+E102)*$C$10+E105*$C$11</f>
+        <v/>
+      </c>
+      <c r="F107" s="28">
+        <f>(F101+F102)*$C$10+F105*$C$11</f>
+        <v/>
+      </c>
+      <c r="G107" s="28">
+        <f>(G101+G102)*$C$10+G105*$C$11</f>
+        <v/>
+      </c>
+      <c r="H107" s="28">
+        <f>(H101+H102)*$C$10+H105*$C$11</f>
+        <v/>
+      </c>
+      <c r="I107" s="28">
+        <f>(I101+I102)*$C$10+I105*$C$11</f>
+        <v/>
+      </c>
+      <c r="J107" s="28">
+        <f>(J101+J102)*$C$10+J105*$C$11</f>
+        <v/>
+      </c>
+      <c r="K107" s="28">
+        <f>(K101+K102)*$C$10+K105*$C$11</f>
+        <v/>
+      </c>
+      <c r="L107" s="27">
+        <f>SUM(C107:K107)</f>
+        <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="17" t="inlineStr">
-        <is>
-          <t>SCENARIO 3: HYPER-PUSH</t>
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>DEAL FLOW (edit these)</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="19" t="inlineStr">
-        <is>
-          <t>Build the €3M machine — staff it like a proven motion</t>
-        </is>
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr"/>
+      <c r="C110" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E110" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F110" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G110" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J110" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K110" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L110" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  capacity guide</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>suggested</t>
+        </is>
+      </c>
+      <c r="C111" s="50">
+        <f>ROUND(C104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="D111" s="50">
+        <f>ROUND(D104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="E111" s="50">
+        <f>ROUND(E104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="F111" s="50">
+        <f>ROUND(F104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="G111" s="50">
+        <f>ROUND(G104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="H111" s="50">
+        <f>ROUND(H104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="I111" s="50">
+        <f>ROUND(I104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="J111" s="50">
+        <f>ROUND(J104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="K111" s="50">
+        <f>ROUND(K104*($C$17+$C$18+$C$19),0)</f>
+        <v/>
+      </c>
+      <c r="L111" s="50">
+        <f>SUM(C111:K111)</f>
+        <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>NARRATIVE</t>
-        </is>
+      <c r="A112" s="23" t="inlineStr">
+        <is>
+          <t>Pilots</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>€15K ARR</t>
+        </is>
+      </c>
+      <c r="C112" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H112" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I112" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J112" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="K112" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L112" s="28">
+        <f>SUM(C112:K112)</f>
+        <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="21" t="inlineStr">
-        <is>
-          <t>Maximum conviction. Victor goes full-time in May. The May large deal anchors Q2. First new AE in June, two more in July, two more in September, another in November. Martijn goes to 0.5 FTE in August. An SMB AE switches to MM in August — no ramp needed. BDR scales to 6 by Q4.</t>
-        </is>
+      <c r="A113" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>€50K ARR</t>
+        </is>
+      </c>
+      <c r="C113" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I113" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K113" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L113" s="28">
+        <f>SUM(C113:K113)</f>
+        <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="21" t="inlineStr">
-        <is>
-          <t>This requires an MM team lead by August — someone who can run pipeline reviews, maintain process quality across 7+ AEs, and own the weekly forecast. We also need solutioning capacity for 3+ large deals in parallel by Q4.</t>
-        </is>
+      <c r="A114" s="23" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>€100K ARR</t>
+        </is>
+      </c>
+      <c r="C114" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" s="28">
+        <f>SUM(C114:K114)</f>
+        <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="21" t="inlineStr">
-        <is>
-          <t>Risk profile: HIGH. Monthly burn hits ~€65K by December. But the output targets €3.3M+ new deal ARR. The SMB switch adds immediate capacity without ramp cost — it's the highest-leverage move if we have the right person.</t>
-        </is>
+      <c r="A115" s="23" t="inlineStr">
+        <is>
+          <t>Total deals</t>
+        </is>
+      </c>
+      <c r="C115" s="27">
+        <f>C112+C113+C114</f>
+        <v/>
+      </c>
+      <c r="D115" s="27">
+        <f>D112+D113+D114</f>
+        <v/>
+      </c>
+      <c r="E115" s="27">
+        <f>E112+E113+E114</f>
+        <v/>
+      </c>
+      <c r="F115" s="27">
+        <f>F112+F113+F114</f>
+        <v/>
+      </c>
+      <c r="G115" s="27">
+        <f>G112+G113+G114</f>
+        <v/>
+      </c>
+      <c r="H115" s="27">
+        <f>H112+H113+H114</f>
+        <v/>
+      </c>
+      <c r="I115" s="27">
+        <f>I112+I113+I114</f>
+        <v/>
+      </c>
+      <c r="J115" s="27">
+        <f>J112+J113+J114</f>
+        <v/>
+      </c>
+      <c r="K115" s="27">
+        <f>K112+K113+K114</f>
+        <v/>
+      </c>
+      <c r="L115" s="27">
+        <f>SUM(C115:K115)</f>
+        <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>HEADCOUNT</t>
+          <t>BDR FUNNEL</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>Ramped: Martijn 0.2→0.5 (Aug), Mossel 0.2, Victor 0.2→1.0 (May), +1 SMB→MM (Aug)</t>
-        </is>
-      </c>
-      <c r="F118" s="46" t="inlineStr">
-        <is>
-          <t>SMB→MM switch: Aug (committed)</t>
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B118" s="22" t="inlineStr"/>
+      <c r="C118" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E118" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G118" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I118" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J118" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K118" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L118" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="22" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B119" s="22" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C119" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D119" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E119" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F119" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G119" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H119" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I119" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J119" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K119" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L119" s="22" t="inlineStr">
-        <is>
-          <t>Peak</t>
-        </is>
+      <c r="A119" s="23" t="inlineStr">
+        <is>
+          <t>Meetings needed /mo</t>
+        </is>
+      </c>
+      <c r="B119" s="24" t="inlineStr">
+        <is>
+          <t>deals ÷ close %</t>
+        </is>
+      </c>
+      <c r="C119" s="28">
+        <f>IF($C$7&gt;0,CEILING(C115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="D119" s="28">
+        <f>IF($C$7&gt;0,CEILING(D115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="E119" s="28">
+        <f>IF($C$7&gt;0,CEILING(E115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="F119" s="28">
+        <f>IF($C$7&gt;0,CEILING(F115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="G119" s="28">
+        <f>IF($C$7&gt;0,CEILING(G115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="H119" s="28">
+        <f>IF($C$7&gt;0,CEILING(H115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="I119" s="28">
+        <f>IF($C$7&gt;0,CEILING(I115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="J119" s="28">
+        <f>IF($C$7&gt;0,CEILING(J115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="K119" s="28">
+        <f>IF($C$7&gt;0,CEILING(K115/$C$7,1),0)</f>
+        <v/>
+      </c>
+      <c r="L119" s="27">
+        <f>SUM(C119:K119)</f>
+        <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="23" t="inlineStr">
         <is>
-          <t>AEs (ramped)</t>
-        </is>
-      </c>
-      <c r="B120" s="24" t="inlineStr">
-        <is>
-          <t>no ramp</t>
-        </is>
-      </c>
-      <c r="C120" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D120" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E120" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F120" s="25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G120" s="25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H120" s="25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I120" s="25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J120" s="25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K120" s="25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L120" s="26" t="n">
-        <v>2.7</v>
+          <t>From SMB BDR (free)</t>
+        </is>
+      </c>
+      <c r="C120" s="51">
+        <f>MIN($C$9,C119)</f>
+        <v/>
+      </c>
+      <c r="D120" s="51">
+        <f>MIN($C$9,D119)</f>
+        <v/>
+      </c>
+      <c r="E120" s="51">
+        <f>MIN($C$9,E119)</f>
+        <v/>
+      </c>
+      <c r="F120" s="51">
+        <f>MIN($C$9,F119)</f>
+        <v/>
+      </c>
+      <c r="G120" s="51">
+        <f>MIN($C$9,G119)</f>
+        <v/>
+      </c>
+      <c r="H120" s="51">
+        <f>MIN($C$9,H119)</f>
+        <v/>
+      </c>
+      <c r="I120" s="51">
+        <f>MIN($C$9,I119)</f>
+        <v/>
+      </c>
+      <c r="J120" s="51">
+        <f>MIN($C$9,J119)</f>
+        <v/>
+      </c>
+      <c r="K120" s="51">
+        <f>MIN($C$9,K119)</f>
+        <v/>
+      </c>
+      <c r="L120" s="51">
+        <f>SUM(C120:K120)</f>
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>AEs (new hires)</t>
+          <t>From dedicated BDRs</t>
         </is>
       </c>
       <c r="B121" s="24" t="inlineStr">
         <is>
-          <t>with ramp</t>
-        </is>
-      </c>
-      <c r="C121" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G121" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H121" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I121" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J121" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K121" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L121" s="26" t="n">
-        <v>6</v>
+          <t>needed /mo</t>
+        </is>
+      </c>
+      <c r="C121" s="28">
+        <f>MAX(0,C119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="D121" s="28">
+        <f>MAX(0,D119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="E121" s="28">
+        <f>MAX(0,E119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="F121" s="28">
+        <f>MAX(0,F119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="G121" s="28">
+        <f>MAX(0,G119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="H121" s="28">
+        <f>MAX(0,H119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="I121" s="28">
+        <f>MAX(0,I119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="J121" s="28">
+        <f>MAX(0,J119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="K121" s="28">
+        <f>MAX(0,K119-$C$9)</f>
+        <v/>
+      </c>
+      <c r="L121" s="27">
+        <f>SUM(C121:K121)</f>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t>Effective AEs</t>
-        </is>
-      </c>
-      <c r="B122" s="24" t="inlineStr">
-        <is>
-          <t>incl. ramp</t>
-        </is>
-      </c>
-      <c r="C122" s="27" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D122" s="27" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="E122" s="27" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="F122" s="27" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="G122" s="27" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="H122" s="27" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="I122" s="27" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="J122" s="27" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="K122" s="27" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="L122" s="26" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="23" t="inlineStr">
-        <is>
-          <t>BDRs (dedicated)</t>
-        </is>
-      </c>
-      <c r="B123" s="24" t="inlineStr">
-        <is>
-          <t>FTE</t>
-        </is>
-      </c>
-      <c r="C123" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D123" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F123" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G123" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H123" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I123" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="J123" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K123" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L123" s="26" t="n">
-        <v>6</v>
+          <t>BDRs needed (peak)</t>
+        </is>
+      </c>
+      <c r="C122" s="27">
+        <f>IF($C$8&gt;0,CEILING(MAX(C121:K121)/$C$8,1),0)</f>
+        <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="23" t="inlineStr">
-        <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="C124" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D124" s="27" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="E124" s="27" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F124" s="27" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="G124" s="27" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="H124" s="27" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="I124" s="27" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="J124" s="27" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="K124" s="27" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="L124" s="26" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>ARR WATERFALL</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="23" t="inlineStr">
-        <is>
-          <t>Monthly cost</t>
-        </is>
-      </c>
-      <c r="C125" s="28" t="inlineStr">
-        <is>
-          <t>€5.2k</t>
-        </is>
-      </c>
-      <c r="D125" s="28" t="inlineStr">
-        <is>
-          <t>€12.4k</t>
-        </is>
-      </c>
-      <c r="E125" s="28" t="inlineStr">
-        <is>
-          <t>€22.4k</t>
-        </is>
-      </c>
-      <c r="F125" s="28" t="inlineStr">
-        <is>
-          <t>€38.4k</t>
-        </is>
-      </c>
-      <c r="G125" s="28" t="inlineStr">
-        <is>
-          <t>€50.2k</t>
-        </is>
-      </c>
-      <c r="H125" s="28" t="inlineStr">
-        <is>
-          <t>€66.2k</t>
-        </is>
-      </c>
-      <c r="I125" s="28" t="inlineStr">
-        <is>
-          <t>€70.2k</t>
-        </is>
-      </c>
-      <c r="J125" s="28" t="inlineStr">
-        <is>
-          <t>€76.2k</t>
-        </is>
-      </c>
-      <c r="K125" s="28" t="inlineStr">
-        <is>
-          <t>€76.2k</t>
-        </is>
-      </c>
-      <c r="L125" s="26" t="inlineStr">
-        <is>
-          <t>€417k total</t>
-        </is>
+      <c r="A125" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B125" s="22" t="inlineStr"/>
+      <c r="C125" s="22" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E125" s="22" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F125" s="22" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G125" s="22" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H125" s="22" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I125" s="22" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J125" s="22" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K125" s="22" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L125" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="23" t="inlineStr">
+        <is>
+          <t>New deal ARR /mo</t>
+        </is>
+      </c>
+      <c r="C126" s="52">
+        <f>C112*$C$4+C113*$C$5+C114*$C$6</f>
+        <v/>
+      </c>
+      <c r="D126" s="52">
+        <f>D112*$C$4+D113*$C$5+D114*$C$6</f>
+        <v/>
+      </c>
+      <c r="E126" s="52">
+        <f>E112*$C$4+E113*$C$5+E114*$C$6</f>
+        <v/>
+      </c>
+      <c r="F126" s="52">
+        <f>F112*$C$4+F113*$C$5+F114*$C$6</f>
+        <v/>
+      </c>
+      <c r="G126" s="52">
+        <f>G112*$C$4+G113*$C$5+G114*$C$6</f>
+        <v/>
+      </c>
+      <c r="H126" s="52">
+        <f>H112*$C$4+H113*$C$5+H114*$C$6</f>
+        <v/>
+      </c>
+      <c r="I126" s="52">
+        <f>I112*$C$4+I113*$C$5+I114*$C$6</f>
+        <v/>
+      </c>
+      <c r="J126" s="52">
+        <f>J112*$C$4+J113*$C$5+J114*$C$6</f>
+        <v/>
+      </c>
+      <c r="K126" s="52">
+        <f>K112*$C$4+K113*$C$5+K114*$C$6</f>
+        <v/>
+      </c>
+      <c r="L126" s="27">
+        <f>SUM(C126:K126)</f>
+        <v/>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>DEAL FLOW</t>
-        </is>
-      </c>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>from AE capacity</t>
-        </is>
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>Cum. new deal ARR</t>
+        </is>
+      </c>
+      <c r="B127" s="24">
+        <f> €2M target</f>
+        <v/>
+      </c>
+      <c r="C127" s="27">
+        <f>C126</f>
+        <v/>
+      </c>
+      <c r="D127" s="27">
+        <f>C127+D126</f>
+        <v/>
+      </c>
+      <c r="E127" s="27">
+        <f>D127+E126</f>
+        <v/>
+      </c>
+      <c r="F127" s="27">
+        <f>E127+F126</f>
+        <v/>
+      </c>
+      <c r="G127" s="27">
+        <f>F127+G126</f>
+        <v/>
+      </c>
+      <c r="H127" s="27">
+        <f>G127+H126</f>
+        <v/>
+      </c>
+      <c r="I127" s="27">
+        <f>H127+I126</f>
+        <v/>
+      </c>
+      <c r="J127" s="27">
+        <f>I127+J126</f>
+        <v/>
+      </c>
+      <c r="K127" s="27">
+        <f>J127+K126</f>
+        <v/>
+      </c>
+      <c r="L127" s="27">
+        <f>K127</f>
+        <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="22" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B128" s="22" t="inlineStr"/>
-      <c r="C128" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D128" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E128" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F128" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G128" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H128" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I128" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J128" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K128" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L128" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="A128" s="23" t="inlineStr">
+        <is>
+          <t>Expansion /mo</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>pilot conv. upside</t>
+        </is>
+      </c>
+      <c r="C128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="54">
+        <f>ROUND(C112*$C$15,0)*($C$5-$C$4)+ROUND(C112*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="I128" s="54">
+        <f>ROUND(D112*$C$15,0)*($C$5-$C$4)+ROUND(D112*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="J128" s="54">
+        <f>ROUND(E112*$C$15,0)*($C$5-$C$4)+ROUND(E112*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="K128" s="54">
+        <f>ROUND(F112*$C$15,0)*($C$5-$C$4)+ROUND(F112*$C$16,0)*($C$6-$C$4)</f>
+        <v/>
+      </c>
+      <c r="L128" s="38">
+        <f>SUM(C128:K128)</f>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="23" t="inlineStr">
         <is>
-          <t>Pilots</t>
+          <t>Total ARR</t>
         </is>
       </c>
       <c r="B129" s="24" t="inlineStr">
         <is>
-          <t>€15K ARR</t>
-        </is>
-      </c>
-      <c r="C129" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E129" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F129" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="G129" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="H129" s="28" t="n">
-        <v>13</v>
-      </c>
-      <c r="I129" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="J129" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="K129" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="L129" s="26" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B130" s="24" t="inlineStr">
-        <is>
-          <t>€50K ARR</t>
-        </is>
-      </c>
-      <c r="C130" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G130" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="H130" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I130" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J130" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="K130" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="L130" s="26" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="23" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="B131" s="24" t="inlineStr">
-        <is>
-          <t>€100K ARR</t>
-        </is>
-      </c>
-      <c r="C131" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="45" t="inlineStr">
-        <is>
-          <t>1*</t>
-        </is>
-      </c>
-      <c r="E131" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="H131" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I131" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J131" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="K131" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L131" s="26" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="23" t="inlineStr">
-        <is>
-          <t>Total deals closing</t>
-        </is>
-      </c>
-      <c r="C132" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E132" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="F132" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="G132" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="H132" s="27" t="n">
-        <v>18</v>
-      </c>
-      <c r="I132" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="J132" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="K132" s="27" t="n">
-        <v>24</v>
-      </c>
-      <c r="L132" s="26" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="24" t="inlineStr">
-        <is>
-          <t>* = deal in pipeline (not from capacity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20" t="inlineStr">
-        <is>
-          <t>PIPELINE NEEDED</t>
-        </is>
-      </c>
-      <c r="B135" s="24" t="inlineStr">
-        <is>
-          <t>2-mo cycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="22" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B136" s="22" t="inlineStr"/>
-      <c r="C136" s="22" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D136" s="22" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E136" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F136" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G136" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H136" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I136" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J136" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K136" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L136" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M136" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N136" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="23" t="inlineStr">
-        <is>
-          <t>Deals closing</t>
-        </is>
-      </c>
-      <c r="B137" s="24" t="inlineStr">
-        <is>
-          <t>when they close</t>
-        </is>
-      </c>
-      <c r="C137" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D137" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E137" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G137" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="H137" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="I137" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="J137" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="K137" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="L137" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="M137" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="N137" s="29" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="23" t="inlineStr">
-        <is>
-          <t>SQLs needed</t>
-        </is>
-      </c>
-      <c r="B138" s="24" t="inlineStr">
-        <is>
-          <t>when to generate</t>
-        </is>
-      </c>
-      <c r="C138" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="D138" s="43" t="n">
-        <v>50</v>
-      </c>
-      <c r="E138" s="43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F138" s="43" t="n">
-        <v>90</v>
-      </c>
-      <c r="G138" s="43" t="n">
-        <v>150</v>
-      </c>
-      <c r="H138" s="43" t="n">
-        <v>180</v>
-      </c>
-      <c r="I138" s="43" t="n">
-        <v>200</v>
-      </c>
-      <c r="J138" s="43" t="n">
-        <v>230</v>
-      </c>
-      <c r="K138" s="43" t="n">
-        <v>240</v>
-      </c>
-      <c r="L138" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M138" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N138" s="44" t="n">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="20" t="inlineStr">
-        <is>
-          <t>ARR WATERFALL</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B141" s="22" t="inlineStr"/>
-      <c r="C141" s="22" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D141" s="22" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="E141" s="22" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="F141" s="22" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="G141" s="22" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="H141" s="22" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="I141" s="22" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="J141" s="22" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="K141" s="22" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="L141" s="22" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="23" t="inlineStr">
-        <is>
-          <t>New deal ARR /mo</t>
-        </is>
-      </c>
-      <c r="C142" s="30" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D142" s="30" t="inlineStr">
-        <is>
-          <t>€195k</t>
-        </is>
-      </c>
-      <c r="E142" s="30" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="F142" s="30" t="inlineStr">
-        <is>
-          <t>€290k</t>
-        </is>
-      </c>
-      <c r="G142" s="30" t="inlineStr">
-        <is>
-          <t>€500k</t>
-        </is>
-      </c>
-      <c r="H142" s="30" t="inlineStr">
-        <is>
-          <t>€545k</t>
-        </is>
-      </c>
-      <c r="I142" s="30" t="inlineStr">
-        <is>
-          <t>€610k</t>
-        </is>
-      </c>
-      <c r="J142" s="30" t="inlineStr">
-        <is>
-          <t>€740k</t>
-        </is>
-      </c>
-      <c r="K142" s="30" t="inlineStr">
-        <is>
-          <t>€755k</t>
-        </is>
-      </c>
-      <c r="L142" s="29" t="inlineStr">
-        <is>
-          <t>€3.86M</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="23" t="inlineStr">
-        <is>
-          <t>Cum. new deal ARR</t>
-        </is>
-      </c>
-      <c r="B143" s="24">
-        <f> €2M target</f>
-        <v/>
-      </c>
-      <c r="C143" s="38" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D143" s="38" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="E143" s="38" t="inlineStr">
-        <is>
-          <t>€420k</t>
-        </is>
-      </c>
-      <c r="F143" s="38" t="inlineStr">
-        <is>
-          <t>€710k</t>
-        </is>
-      </c>
-      <c r="G143" s="38" t="inlineStr">
-        <is>
-          <t>€1.21M</t>
-        </is>
-      </c>
-      <c r="H143" s="38" t="inlineStr">
-        <is>
-          <t>€1.75M</t>
-        </is>
-      </c>
-      <c r="I143" s="38" t="inlineStr">
-        <is>
-          <t>€2.37M</t>
-        </is>
-      </c>
-      <c r="J143" s="38" t="inlineStr">
-        <is>
-          <t>€3.10M</t>
-        </is>
-      </c>
-      <c r="K143" s="38" t="inlineStr">
-        <is>
-          <t>€3.86M</t>
-        </is>
-      </c>
-      <c r="L143" s="41" t="inlineStr">
-        <is>
-          <t>€3.86M</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="23" t="inlineStr">
-        <is>
-          <t>Expansion /mo</t>
-        </is>
-      </c>
-      <c r="B144" s="24" t="inlineStr">
-        <is>
-          <t>upside</t>
-        </is>
-      </c>
-      <c r="C144" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D144" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E144" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I144" s="34" t="inlineStr">
-        <is>
-          <t>€35k</t>
-        </is>
-      </c>
-      <c r="J144" s="34" t="inlineStr">
-        <is>
-          <t>€70k</t>
-        </is>
-      </c>
-      <c r="K144" s="34" t="inlineStr">
-        <is>
-          <t>€155k</t>
-        </is>
-      </c>
-      <c r="L144" s="42" t="inlineStr">
-        <is>
-          <t>+€260k</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="23" t="inlineStr">
-        <is>
-          <t>Total ARR</t>
-        </is>
-      </c>
-      <c r="C145" s="35" t="inlineStr">
-        <is>
-          <t>€15k</t>
-        </is>
-      </c>
-      <c r="D145" s="35" t="inlineStr">
-        <is>
-          <t>€210k</t>
-        </is>
-      </c>
-      <c r="E145" s="35" t="inlineStr">
-        <is>
-          <t>€420k</t>
-        </is>
-      </c>
-      <c r="F145" s="35" t="inlineStr">
-        <is>
-          <t>€710k</t>
-        </is>
-      </c>
-      <c r="G145" s="35" t="inlineStr">
-        <is>
-          <t>€1.21M</t>
-        </is>
-      </c>
-      <c r="H145" s="35" t="inlineStr">
-        <is>
-          <t>€1.75M</t>
-        </is>
-      </c>
-      <c r="I145" s="35" t="inlineStr">
-        <is>
-          <t>€2.40M</t>
-        </is>
-      </c>
-      <c r="J145" s="35" t="inlineStr">
-        <is>
-          <t>€3.21M</t>
-        </is>
-      </c>
-      <c r="K145" s="35" t="inlineStr">
-        <is>
-          <t>€4.12M</t>
-        </is>
-      </c>
-      <c r="L145" s="36" t="inlineStr">
-        <is>
-          <t>€4.12M</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="20" t="inlineStr">
-        <is>
-          <t>BDR FUNNEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="18" t="inlineStr">
-        <is>
-          <t>121 deals ÷ 10% = 1210 meetings over 9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="18">
-        <f> 135/mo − 15 from SMB BDRs = 120 from dedicated BDRs</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="37" t="inlineStr">
-        <is>
-          <t>120/mo ÷ 15/BDR = 8 dedicated MM BDRs needed</t>
-        </is>
+          <t>incl. expansion</t>
+        </is>
+      </c>
+      <c r="C129" s="35">
+        <f>C126+C128</f>
+        <v/>
+      </c>
+      <c r="D129" s="35">
+        <f>C129+D126+D128</f>
+        <v/>
+      </c>
+      <c r="E129" s="35">
+        <f>D129+E126+E128</f>
+        <v/>
+      </c>
+      <c r="F129" s="35">
+        <f>E129+F126+F128</f>
+        <v/>
+      </c>
+      <c r="G129" s="35">
+        <f>F129+G126+G128</f>
+        <v/>
+      </c>
+      <c r="H129" s="35">
+        <f>G129+H126+H128</f>
+        <v/>
+      </c>
+      <c r="I129" s="35">
+        <f>H129+I126+I128</f>
+        <v/>
+      </c>
+      <c r="J129" s="35">
+        <f>I129+J126+J128</f>
+        <v/>
+      </c>
+      <c r="K129" s="35">
+        <f>J129+K126+K128</f>
+        <v/>
+      </c>
+      <c r="L129" s="35">
+        <f>K129</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A114:K114"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A113:K113"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A5:K5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A97:K97"/>
     <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A115:K115"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A67:K67"/>
+    <mergeCell ref="A60:K60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
